--- a/research/traditional_assets/database/data/spain/spain_hospitals_healthcare_facilities.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_hospitals_healthcare_facilities.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08231483628375177</v>
+        <v>0.08214279919304239</v>
       </c>
       <c r="C2">
-        <v>578.675983312805</v>
+        <v>575.0155021294194</v>
       </c>
       <c r="D2">
-        <v>542.675983312805</v>
+        <v>544.8655021294194</v>
       </c>
       <c r="E2">
-        <v>-68.59999999999999</v>
+        <v>-62.74999999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.850000000000001</v>
       </c>
       <c r="G2">
         <v>36</v>
@@ -1451,28 +1451,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.294255</v>
       </c>
       <c r="N2">
-        <v>56.59999999999999</v>
+        <v>56.30574499999999</v>
       </c>
       <c r="O2">
-        <v>14.15</v>
+        <v>14.07643625</v>
       </c>
       <c r="P2">
-        <v>42.45</v>
+        <v>42.22930874999999</v>
       </c>
       <c r="Q2">
-        <v>64.44999999999999</v>
+        <v>64.22930875</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08231483628375177</v>
+        <v>0.08259146383135596</v>
       </c>
       <c r="T2">
-        <v>0.5648729042001043</v>
+        <v>0.5691522443834384</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>192.3501724694568</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08214279919304239</v>
+        <v>0.08197076210233303</v>
       </c>
       <c r="C3">
-        <v>575.0155021294194</v>
+        <v>571.3727604935087</v>
       </c>
       <c r="D3">
-        <v>544.8655021294194</v>
+        <v>547.0727604935088</v>
       </c>
       <c r="E3">
-        <v>-62.74999999999999</v>
+        <v>-56.89999999999999</v>
       </c>
       <c r="F3">
-        <v>5.850000000000001</v>
+        <v>11.7</v>
       </c>
       <c r="G3">
         <v>36</v>
@@ -1533,28 +1533,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M3">
-        <v>0.294255</v>
+        <v>0.58851</v>
       </c>
       <c r="N3">
-        <v>56.30574499999999</v>
+        <v>56.01148999999999</v>
       </c>
       <c r="O3">
-        <v>14.07643625</v>
+        <v>14.0028725</v>
       </c>
       <c r="P3">
-        <v>42.22930874999999</v>
+        <v>42.0086175</v>
       </c>
       <c r="Q3">
-        <v>64.22930875</v>
+        <v>64.0086175</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08259146383135596</v>
+        <v>0.08287373683911534</v>
       </c>
       <c r="T3">
-        <v>0.5691522443834384</v>
+        <v>0.5735189180399018</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>192.3501724694568</v>
+        <v>96.17508623472838</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08197076210233303</v>
+        <v>0.08179872501162364</v>
       </c>
       <c r="C4">
-        <v>571.3727604935087</v>
+        <v>567.7479748715054</v>
       </c>
       <c r="D4">
-        <v>547.0727604935088</v>
+        <v>549.2979748715054</v>
       </c>
       <c r="E4">
-        <v>-56.89999999999999</v>
+        <v>-51.05</v>
       </c>
       <c r="F4">
-        <v>11.7</v>
+        <v>17.55</v>
       </c>
       <c r="G4">
         <v>36</v>
@@ -1615,28 +1615,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M4">
-        <v>0.58851</v>
+        <v>0.882765</v>
       </c>
       <c r="N4">
-        <v>56.01148999999999</v>
+        <v>55.717235</v>
       </c>
       <c r="O4">
-        <v>14.0028725</v>
+        <v>13.92930875</v>
       </c>
       <c r="P4">
-        <v>42.0086175</v>
+        <v>41.78792625</v>
       </c>
       <c r="Q4">
-        <v>64.0086175</v>
+        <v>63.78792625</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08287373683911534</v>
+        <v>0.08316182990889034</v>
       </c>
       <c r="T4">
-        <v>0.5735189180399018</v>
+        <v>0.5779756262047459</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>96.17508623472838</v>
+        <v>64.11672415648559</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08179872501162364</v>
+        <v>0.08162668792091425</v>
       </c>
       <c r="C5">
-        <v>567.7479748715054</v>
+        <v>564.1413652661265</v>
       </c>
       <c r="D5">
-        <v>549.2979748715054</v>
+        <v>551.5413652661265</v>
       </c>
       <c r="E5">
-        <v>-51.05</v>
+        <v>-45.19999999999999</v>
       </c>
       <c r="F5">
-        <v>17.55</v>
+        <v>23.4</v>
       </c>
       <c r="G5">
         <v>36</v>
@@ -1697,28 +1697,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M5">
-        <v>0.882765</v>
+        <v>1.17702</v>
       </c>
       <c r="N5">
-        <v>55.717235</v>
+        <v>55.42298</v>
       </c>
       <c r="O5">
-        <v>13.92930875</v>
+        <v>13.855745</v>
       </c>
       <c r="P5">
-        <v>41.78792625</v>
+        <v>41.567235</v>
       </c>
       <c r="Q5">
-        <v>63.78792625</v>
+        <v>63.567235</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08316182990889034</v>
+        <v>0.08345592491761902</v>
       </c>
       <c r="T5">
-        <v>0.5779756262047459</v>
+        <v>0.5825251824563575</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>64.11672415648559</v>
+        <v>48.08754311736419</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08162668792091425</v>
+        <v>0.08145465083020488</v>
       </c>
       <c r="C6">
-        <v>564.1413652661265</v>
+        <v>560.553155288885</v>
       </c>
       <c r="D6">
-        <v>551.5413652661265</v>
+        <v>553.803155288885</v>
       </c>
       <c r="E6">
-        <v>-45.19999999999999</v>
+        <v>-39.34999999999999</v>
       </c>
       <c r="F6">
-        <v>23.4</v>
+        <v>29.25</v>
       </c>
       <c r="G6">
         <v>36</v>
@@ -1779,28 +1779,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M6">
-        <v>1.17702</v>
+        <v>1.471275</v>
       </c>
       <c r="N6">
-        <v>55.42298</v>
+        <v>55.128725</v>
       </c>
       <c r="O6">
-        <v>13.855745</v>
+        <v>13.78218125</v>
       </c>
       <c r="P6">
-        <v>41.567235</v>
+        <v>41.34654375</v>
       </c>
       <c r="Q6">
-        <v>63.567235</v>
+        <v>63.34654375</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08345592491761902</v>
+        <v>0.08375621140021566</v>
       </c>
       <c r="T6">
-        <v>0.5825251824563575</v>
+        <v>0.587170518839582</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>48.08754311736419</v>
+        <v>38.47003449389135</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08145465083020488</v>
+        <v>0.0812826137394955</v>
       </c>
       <c r="C7">
-        <v>560.553155288885</v>
+        <v>556.9835722343898</v>
       </c>
       <c r="D7">
-        <v>553.803155288885</v>
+        <v>556.0835722343899</v>
       </c>
       <c r="E7">
-        <v>-39.34999999999999</v>
+        <v>-33.49999999999999</v>
       </c>
       <c r="F7">
-        <v>29.25</v>
+        <v>35.1</v>
       </c>
       <c r="G7">
         <v>36</v>
@@ -1861,28 +1861,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M7">
-        <v>1.471275</v>
+        <v>1.76553</v>
       </c>
       <c r="N7">
-        <v>55.128725</v>
+        <v>54.83447</v>
       </c>
       <c r="O7">
-        <v>13.78218125</v>
+        <v>13.7086175</v>
       </c>
       <c r="P7">
-        <v>41.34654375</v>
+        <v>41.12585249999999</v>
       </c>
       <c r="Q7">
-        <v>63.34654375</v>
+        <v>63.12585249999999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08375621140021566</v>
+        <v>0.08406288695691011</v>
       </c>
       <c r="T7">
-        <v>0.587170518839582</v>
+        <v>0.5919146921671306</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>38.47003449389135</v>
+        <v>32.05836207824279</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0812826137394955</v>
+        <v>0.08111057664878611</v>
       </c>
       <c r="C8">
-        <v>556.9835722343898</v>
+        <v>553.4328471564886</v>
       </c>
       <c r="D8">
-        <v>556.0835722343899</v>
+        <v>558.3828471564887</v>
       </c>
       <c r="E8">
-        <v>-33.49999999999999</v>
+        <v>-27.65</v>
       </c>
       <c r="F8">
-        <v>35.1</v>
+        <v>40.95</v>
       </c>
       <c r="G8">
         <v>36</v>
@@ -1943,28 +1943,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M8">
-        <v>1.76553</v>
+        <v>2.059785</v>
       </c>
       <c r="N8">
-        <v>54.83447</v>
+        <v>54.540215</v>
       </c>
       <c r="O8">
-        <v>13.7086175</v>
+        <v>13.63505375</v>
       </c>
       <c r="P8">
-        <v>41.12585249999999</v>
+        <v>40.90516125</v>
       </c>
       <c r="Q8">
-        <v>63.12585249999999</v>
+        <v>62.90516125</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08406288695691011</v>
+        <v>0.08437615768686679</v>
       </c>
       <c r="T8">
-        <v>0.5919146921671306</v>
+        <v>0.5967608907275295</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>32.05836207824279</v>
+        <v>27.47859606706525</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08111057664878611</v>
+        <v>0.08093853955807673</v>
       </c>
       <c r="C9">
-        <v>553.4328471564886</v>
+        <v>549.901214946309</v>
       </c>
       <c r="D9">
-        <v>558.3828471564887</v>
+        <v>560.7012149463089</v>
       </c>
       <c r="E9">
-        <v>-27.64999999999999</v>
+        <v>-21.79999999999999</v>
       </c>
       <c r="F9">
-        <v>40.95</v>
+        <v>46.8</v>
       </c>
       <c r="G9">
         <v>36</v>
@@ -2025,28 +2025,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M9">
-        <v>2.059785</v>
+        <v>2.35404</v>
       </c>
       <c r="N9">
-        <v>54.540215</v>
+        <v>54.24596</v>
       </c>
       <c r="O9">
-        <v>13.63505375</v>
+        <v>13.56149</v>
       </c>
       <c r="P9">
-        <v>40.90516125</v>
+        <v>40.68447</v>
       </c>
       <c r="Q9">
-        <v>62.90516125</v>
+        <v>62.68447</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08437615768686679</v>
+        <v>0.08469623865008341</v>
       </c>
       <c r="T9">
-        <v>0.5967608907275295</v>
+        <v>0.6017124414305459</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.47859606706525</v>
+        <v>24.0437715586821</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08093853955807673</v>
+        <v>0.08076650246736736</v>
       </c>
       <c r="C10">
-        <v>549.901214946309</v>
+        <v>546.3889144122504</v>
       </c>
       <c r="D10">
-        <v>560.7012149463089</v>
+        <v>563.0389144122504</v>
       </c>
       <c r="E10">
-        <v>-21.79999999999999</v>
+        <v>-15.95</v>
       </c>
       <c r="F10">
-        <v>46.8</v>
+        <v>52.65</v>
       </c>
       <c r="G10">
         <v>36</v>
@@ -2107,28 +2107,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M10">
-        <v>2.35404</v>
+        <v>2.648295</v>
       </c>
       <c r="N10">
-        <v>54.24596</v>
+        <v>53.951705</v>
       </c>
       <c r="O10">
-        <v>13.56149</v>
+        <v>13.48792625</v>
       </c>
       <c r="P10">
-        <v>40.68447</v>
+        <v>40.46377875</v>
       </c>
       <c r="Q10">
-        <v>62.68447</v>
+        <v>62.46377875</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08469623865008341</v>
+        <v>0.08502335435974434</v>
       </c>
       <c r="T10">
-        <v>0.6017124414305459</v>
+        <v>0.6067728174237383</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.0437715586821</v>
+        <v>21.3722413854952</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08076650246736736</v>
+        <v>0.08059446537665799</v>
       </c>
       <c r="C11">
-        <v>546.3889144122504</v>
+        <v>542.896188361988</v>
       </c>
       <c r="D11">
-        <v>563.0389144122504</v>
+        <v>565.396188361988</v>
       </c>
       <c r="E11">
-        <v>-15.95</v>
+        <v>-10.1</v>
       </c>
       <c r="F11">
-        <v>52.65</v>
+        <v>58.49999999999999</v>
       </c>
       <c r="G11">
         <v>36</v>
@@ -2189,28 +2189,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M11">
-        <v>2.648295</v>
+        <v>2.942549999999999</v>
       </c>
       <c r="N11">
-        <v>53.951705</v>
+        <v>53.65745</v>
       </c>
       <c r="O11">
-        <v>13.48792625</v>
+        <v>13.4143625</v>
       </c>
       <c r="P11">
-        <v>40.46377875</v>
+        <v>40.2430875</v>
       </c>
       <c r="Q11">
-        <v>62.46377875</v>
+        <v>62.2430875</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08502335435974434</v>
+        <v>0.08535773930739776</v>
       </c>
       <c r="T11">
-        <v>0.6067728174237383</v>
+        <v>0.6119456462167796</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.3722413854952</v>
+        <v>19.23501724694568</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08059446537665799</v>
+        <v>0.0804224282859486</v>
       </c>
       <c r="C12">
-        <v>542.896188361988</v>
+        <v>539.423283686542</v>
       </c>
       <c r="D12">
-        <v>565.396188361988</v>
+        <v>567.7732836865421</v>
       </c>
       <c r="E12">
-        <v>-10.09999999999999</v>
+        <v>-4.25</v>
       </c>
       <c r="F12">
-        <v>58.5</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="G12">
         <v>36</v>
@@ -2271,28 +2271,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M12">
-        <v>2.94255</v>
+        <v>3.236804999999999</v>
       </c>
       <c r="N12">
-        <v>53.65745</v>
+        <v>53.363195</v>
       </c>
       <c r="O12">
-        <v>13.4143625</v>
+        <v>13.34079875</v>
       </c>
       <c r="P12">
-        <v>40.2430875</v>
+        <v>40.02239625</v>
       </c>
       <c r="Q12">
-        <v>62.2430875</v>
+        <v>62.02239625</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08535773930739776</v>
+        <v>0.08569963852353776</v>
       </c>
       <c r="T12">
-        <v>0.6119456462167796</v>
+        <v>0.6172347183534848</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.23501724694568</v>
+        <v>17.48637931540516</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0804224282859486</v>
+        <v>0.08025039119523923</v>
       </c>
       <c r="C13">
-        <v>539.423283686542</v>
+        <v>535.9704514464783</v>
       </c>
       <c r="D13">
-        <v>567.7732836865421</v>
+        <v>570.1704514464783</v>
       </c>
       <c r="E13">
-        <v>-4.25</v>
+        <v>1.600000000000009</v>
       </c>
       <c r="F13">
-        <v>64.34999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="G13">
         <v>36</v>
@@ -2353,28 +2353,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M13">
-        <v>3.236804999999999</v>
+        <v>3.53106</v>
       </c>
       <c r="N13">
-        <v>53.363195</v>
+        <v>53.06894</v>
       </c>
       <c r="O13">
-        <v>13.34079875</v>
+        <v>13.267235</v>
       </c>
       <c r="P13">
-        <v>40.02239625</v>
+        <v>39.801705</v>
       </c>
       <c r="Q13">
-        <v>62.02239625</v>
+        <v>61.801705</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08569963852353776</v>
+        <v>0.08604930817640821</v>
       </c>
       <c r="T13">
-        <v>0.6172347183534848</v>
+        <v>0.6226439966751149</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.48637931540516</v>
+        <v>16.0291810391214</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08025039119523923</v>
+        <v>0.08007835410452983</v>
       </c>
       <c r="C14">
-        <v>535.9704514464783</v>
+        <v>532.5379469603027</v>
       </c>
       <c r="D14">
-        <v>570.1704514464783</v>
+        <v>572.5879469603027</v>
       </c>
       <c r="E14">
-        <v>1.600000000000009</v>
+        <v>7.450000000000003</v>
       </c>
       <c r="F14">
-        <v>70.2</v>
+        <v>76.05</v>
       </c>
       <c r="G14">
         <v>36</v>
@@ -2435,28 +2435,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M14">
-        <v>3.53106</v>
+        <v>3.825315</v>
       </c>
       <c r="N14">
-        <v>53.06894</v>
+        <v>52.77468499999999</v>
       </c>
       <c r="O14">
-        <v>13.267235</v>
+        <v>13.19367125</v>
       </c>
       <c r="P14">
-        <v>39.801705</v>
+        <v>39.58101375</v>
       </c>
       <c r="Q14">
-        <v>61.801705</v>
+        <v>61.58101375</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08604930817640821</v>
+        <v>0.08640701621210325</v>
       </c>
       <c r="T14">
-        <v>0.6226439966751149</v>
+        <v>0.6281776262225297</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.0291810391214</v>
+        <v>14.79616711303513</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08007835410452983</v>
+        <v>0.07990631701382046</v>
       </c>
       <c r="C15">
-        <v>532.5379469603027</v>
+        <v>529.1260298951107</v>
       </c>
       <c r="D15">
-        <v>572.5879469603027</v>
+        <v>575.0260298951107</v>
       </c>
       <c r="E15">
-        <v>7.450000000000003</v>
+        <v>13.30000000000001</v>
       </c>
       <c r="F15">
-        <v>76.05</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="G15">
         <v>36</v>
@@ -2517,28 +2517,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M15">
-        <v>3.825315</v>
+        <v>4.11957</v>
       </c>
       <c r="N15">
-        <v>52.77468499999999</v>
+        <v>52.48042999999999</v>
       </c>
       <c r="O15">
-        <v>13.19367125</v>
+        <v>13.1201075</v>
       </c>
       <c r="P15">
-        <v>39.58101375</v>
+        <v>39.3603225</v>
       </c>
       <c r="Q15">
-        <v>61.58101375</v>
+        <v>61.3603225</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08640701621210325</v>
+        <v>0.08677304303932612</v>
       </c>
       <c r="T15">
-        <v>0.6281776262225297</v>
+        <v>0.6338399448291868</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.79616711303513</v>
+        <v>13.73929803353262</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07990631701382046</v>
+        <v>0.07990302992311107</v>
       </c>
       <c r="C16">
-        <v>529.1260298951107</v>
+        <v>523.3228161961563</v>
       </c>
       <c r="D16">
-        <v>575.0260298951107</v>
+        <v>575.0728161961563</v>
       </c>
       <c r="E16">
-        <v>13.30000000000001</v>
+        <v>19.15000000000002</v>
       </c>
       <c r="F16">
-        <v>81.90000000000001</v>
+        <v>87.75000000000001</v>
       </c>
       <c r="G16">
         <v>36</v>
@@ -2599,45 +2599,45 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M16">
-        <v>4.11957</v>
+        <v>4.545450000000001</v>
       </c>
       <c r="N16">
-        <v>52.48042999999999</v>
+        <v>52.05454999999999</v>
       </c>
       <c r="O16">
-        <v>13.1201075</v>
+        <v>13.0136375</v>
       </c>
       <c r="P16">
-        <v>39.3603225</v>
+        <v>39.04091249999999</v>
       </c>
       <c r="Q16">
-        <v>61.3603225</v>
+        <v>61.04091249999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08677304303932612</v>
+        <v>0.08714768226248362</v>
       </c>
       <c r="T16">
-        <v>0.6338399448291868</v>
+        <v>0.6396354944618827</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.73929803353262</v>
+        <v>12.45201245201245</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07990302992311107</v>
+        <v>0.07974224283240171</v>
       </c>
       <c r="C17">
-        <v>523.3228161961563</v>
+        <v>519.770686036533</v>
       </c>
       <c r="D17">
-        <v>575.0728161961563</v>
+        <v>577.370686036533</v>
       </c>
       <c r="E17">
-        <v>19.15000000000001</v>
+        <v>25.00000000000001</v>
       </c>
       <c r="F17">
-        <v>87.75</v>
+        <v>93.60000000000001</v>
       </c>
       <c r="G17">
         <v>36</v>
@@ -2681,28 +2681,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M17">
-        <v>4.54545</v>
+        <v>4.84848</v>
       </c>
       <c r="N17">
-        <v>52.05454999999999</v>
+        <v>51.75151999999999</v>
       </c>
       <c r="O17">
-        <v>13.0136375</v>
+        <v>12.93788</v>
       </c>
       <c r="P17">
-        <v>39.04091249999999</v>
+        <v>38.81363999999999</v>
       </c>
       <c r="Q17">
-        <v>61.04091249999999</v>
+        <v>60.81363999999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08714768226248362</v>
+        <v>0.08753124146714489</v>
       </c>
       <c r="T17">
-        <v>0.6396354944618827</v>
+        <v>0.6455690333715477</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.45201245201245</v>
+        <v>11.67376167376167</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07974224283240171</v>
+        <v>0.07958145574169233</v>
       </c>
       <c r="C18">
-        <v>519.770686036533</v>
+        <v>516.2369931561133</v>
       </c>
       <c r="D18">
-        <v>577.370686036533</v>
+        <v>579.6869931561133</v>
       </c>
       <c r="E18">
-        <v>25.00000000000001</v>
+        <v>30.85000000000001</v>
       </c>
       <c r="F18">
-        <v>93.60000000000001</v>
+        <v>99.45</v>
       </c>
       <c r="G18">
         <v>36</v>
@@ -2763,28 +2763,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M18">
-        <v>4.84848</v>
+        <v>5.15151</v>
       </c>
       <c r="N18">
-        <v>51.75151999999999</v>
+        <v>51.44848999999999</v>
       </c>
       <c r="O18">
-        <v>12.93788</v>
+        <v>12.8621225</v>
       </c>
       <c r="P18">
-        <v>38.81363999999999</v>
+        <v>38.58636749999999</v>
       </c>
       <c r="Q18">
-        <v>60.81363999999999</v>
+        <v>60.58636749999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08753124146714489</v>
+        <v>0.08792404306227991</v>
       </c>
       <c r="T18">
-        <v>0.6455690333715477</v>
+        <v>0.6516455491224096</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.67376167376167</v>
+        <v>10.98706981059922</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07958145574169233</v>
+        <v>0.07942066865098293</v>
       </c>
       <c r="C19">
-        <v>516.2369931561133</v>
+        <v>512.7219603498327</v>
       </c>
       <c r="D19">
-        <v>579.6869931561133</v>
+        <v>582.0219603498326</v>
       </c>
       <c r="E19">
-        <v>30.85000000000001</v>
+        <v>36.70000000000002</v>
       </c>
       <c r="F19">
-        <v>99.45</v>
+        <v>105.3</v>
       </c>
       <c r="G19">
         <v>36</v>
@@ -2845,28 +2845,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M19">
-        <v>5.15151</v>
+        <v>5.454540000000001</v>
       </c>
       <c r="N19">
-        <v>51.44848999999999</v>
+        <v>51.14545999999999</v>
       </c>
       <c r="O19">
-        <v>12.8621225</v>
+        <v>12.786365</v>
       </c>
       <c r="P19">
-        <v>38.58636749999999</v>
+        <v>38.359095</v>
       </c>
       <c r="Q19">
-        <v>60.58636749999999</v>
+        <v>60.359095</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08792404306227991</v>
+        <v>0.08832642518412553</v>
       </c>
       <c r="T19">
-        <v>0.6516455491224096</v>
+        <v>0.6578702725745117</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.98706981059922</v>
+        <v>10.37667704334371</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07942066865098295</v>
+        <v>0.07925988156027357</v>
       </c>
       <c r="C20">
-        <v>512.7219603498326</v>
+        <v>509.225814016797</v>
       </c>
       <c r="D20">
-        <v>582.0219603498325</v>
+        <v>584.375814016797</v>
       </c>
       <c r="E20">
-        <v>36.7</v>
+        <v>42.55000000000001</v>
       </c>
       <c r="F20">
-        <v>105.3</v>
+        <v>111.15</v>
       </c>
       <c r="G20">
         <v>36</v>
@@ -2927,28 +2927,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M20">
-        <v>5.45454</v>
+        <v>5.75757</v>
       </c>
       <c r="N20">
-        <v>51.14545999999999</v>
+        <v>50.84242999999999</v>
       </c>
       <c r="O20">
-        <v>12.786365</v>
+        <v>12.7106075</v>
       </c>
       <c r="P20">
-        <v>38.359095</v>
+        <v>38.1318225</v>
       </c>
       <c r="Q20">
-        <v>60.359095</v>
+        <v>60.1318225</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08832642518412553</v>
+        <v>0.08873874266700441</v>
       </c>
       <c r="T20">
-        <v>0.6578702725745117</v>
+        <v>0.6642486929019745</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.37667704334371</v>
+        <v>9.830536146325619</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07925988156027357</v>
+        <v>0.07935409446956419</v>
       </c>
       <c r="C21">
-        <v>509.225814016797</v>
+        <v>501.9942735328688</v>
       </c>
       <c r="D21">
-        <v>584.375814016797</v>
+        <v>582.9942735328688</v>
       </c>
       <c r="E21">
-        <v>42.55000000000001</v>
+        <v>48.40000000000001</v>
       </c>
       <c r="F21">
-        <v>111.15</v>
+        <v>117</v>
       </c>
       <c r="G21">
         <v>36</v>
@@ -3009,45 +3009,45 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M21">
-        <v>5.75757</v>
+        <v>6.2595</v>
       </c>
       <c r="N21">
-        <v>50.84242999999999</v>
+        <v>50.34049999999999</v>
       </c>
       <c r="O21">
-        <v>12.7106075</v>
+        <v>12.585125</v>
       </c>
       <c r="P21">
-        <v>38.1318225</v>
+        <v>37.75537499999999</v>
       </c>
       <c r="Q21">
-        <v>60.1318225</v>
+        <v>59.75537499999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08873874266700441</v>
+        <v>0.08916136808695524</v>
       </c>
       <c r="T21">
-        <v>0.6642486929019745</v>
+        <v>0.6707865737376238</v>
       </c>
       <c r="U21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>9.830536146325619</v>
+        <v>9.042255771227733</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07935409446956419</v>
+        <v>0.07920605737885481</v>
       </c>
       <c r="C22">
-        <v>501.9942735328688</v>
+        <v>498.3180360939755</v>
       </c>
       <c r="D22">
-        <v>582.9942735328688</v>
+        <v>585.1680360939755</v>
       </c>
       <c r="E22">
-        <v>48.40000000000001</v>
+        <v>54.25000000000001</v>
       </c>
       <c r="F22">
-        <v>117</v>
+        <v>122.85</v>
       </c>
       <c r="G22">
         <v>36</v>
@@ -3091,28 +3091,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M22">
-        <v>6.2595</v>
+        <v>6.572475000000001</v>
       </c>
       <c r="N22">
-        <v>50.34049999999999</v>
+        <v>50.027525</v>
       </c>
       <c r="O22">
-        <v>12.585125</v>
+        <v>12.50688125</v>
       </c>
       <c r="P22">
-        <v>37.75537499999999</v>
+        <v>37.52064375</v>
       </c>
       <c r="Q22">
-        <v>59.75537499999999</v>
+        <v>59.52064375</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08916136808695524</v>
+        <v>0.08959469288462633</v>
       </c>
       <c r="T22">
-        <v>0.6707865737376238</v>
+        <v>0.6774899705437959</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.042255771227733</v>
+        <v>8.611672163074031</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07920605737885481</v>
+        <v>0.07905802028814542</v>
       </c>
       <c r="C23">
-        <v>498.3180360939755</v>
+        <v>494.6580695807222</v>
       </c>
       <c r="D23">
-        <v>585.1680360939755</v>
+        <v>587.3580695807221</v>
       </c>
       <c r="E23">
-        <v>54.25</v>
+        <v>60.09999999999999</v>
       </c>
       <c r="F23">
-        <v>122.85</v>
+        <v>128.7</v>
       </c>
       <c r="G23">
         <v>36</v>
@@ -3173,28 +3173,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M23">
-        <v>6.572475</v>
+        <v>6.88545</v>
       </c>
       <c r="N23">
-        <v>50.027525</v>
+        <v>49.71455</v>
       </c>
       <c r="O23">
-        <v>12.50688125</v>
+        <v>12.4286375</v>
       </c>
       <c r="P23">
-        <v>37.52064375</v>
+        <v>37.28591249999999</v>
       </c>
       <c r="Q23">
-        <v>59.52064375</v>
+        <v>59.28591249999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08959469288462633</v>
+        <v>0.09003912857454541</v>
       </c>
       <c r="T23">
-        <v>0.6774899705437959</v>
+        <v>0.684365249319357</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.611672163074033</v>
+        <v>8.220232519297941</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07905802028814542</v>
+        <v>0.07890998319743606</v>
       </c>
       <c r="C24">
-        <v>494.6580695807222</v>
+        <v>491.0145573647201</v>
       </c>
       <c r="D24">
-        <v>587.3580695807221</v>
+        <v>589.5645573647201</v>
       </c>
       <c r="E24">
-        <v>60.09999999999999</v>
+        <v>65.95000000000002</v>
       </c>
       <c r="F24">
-        <v>128.7</v>
+        <v>134.55</v>
       </c>
       <c r="G24">
         <v>36</v>
@@ -3255,28 +3255,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M24">
-        <v>6.88545</v>
+        <v>7.198425</v>
       </c>
       <c r="N24">
-        <v>49.71455</v>
+        <v>49.40157499999999</v>
       </c>
       <c r="O24">
-        <v>12.4286375</v>
+        <v>12.35039375</v>
       </c>
       <c r="P24">
-        <v>37.28591249999999</v>
+        <v>37.05118125</v>
       </c>
       <c r="Q24">
-        <v>59.28591249999999</v>
+        <v>59.05118125</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09003912857454541</v>
+        <v>0.09049510804861824</v>
       </c>
       <c r="T24">
-        <v>0.684365249319357</v>
+        <v>0.6914191067644133</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.220232519297941</v>
+        <v>7.862831105415419</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07890998319743606</v>
+        <v>0.07890594610672667</v>
       </c>
       <c r="C25">
-        <v>491.0145573647201</v>
+        <v>485.2249622988624</v>
       </c>
       <c r="D25">
-        <v>589.5645573647201</v>
+        <v>589.6249622988623</v>
       </c>
       <c r="E25">
-        <v>65.95000000000002</v>
+        <v>71.80000000000001</v>
       </c>
       <c r="F25">
-        <v>134.55</v>
+        <v>140.4</v>
       </c>
       <c r="G25">
         <v>36</v>
@@ -3337,45 +3337,45 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M25">
-        <v>7.198425</v>
+        <v>7.62372</v>
       </c>
       <c r="N25">
-        <v>49.40157499999999</v>
+        <v>48.97628</v>
       </c>
       <c r="O25">
-        <v>12.35039375</v>
+        <v>12.24407</v>
       </c>
       <c r="P25">
-        <v>37.05118125</v>
+        <v>36.73220999999999</v>
       </c>
       <c r="Q25">
-        <v>59.05118125</v>
+        <v>58.73220999999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09049510804861824</v>
+        <v>0.09096308698253509</v>
       </c>
       <c r="T25">
-        <v>0.6914191067644133</v>
+        <v>0.6986585920369711</v>
       </c>
       <c r="U25">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y25">
-        <v>7.862831105415419</v>
+        <v>7.424197111121604</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07890594610672667</v>
+        <v>0.07876390901601729</v>
       </c>
       <c r="C26">
-        <v>485.2249622988624</v>
+        <v>481.5080981670707</v>
       </c>
       <c r="D26">
-        <v>589.6249622988623</v>
+        <v>591.7580981670707</v>
       </c>
       <c r="E26">
-        <v>71.80000000000001</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="F26">
-        <v>140.4</v>
+        <v>146.25</v>
       </c>
       <c r="G26">
         <v>36</v>
@@ -3419,28 +3419,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M26">
-        <v>7.62372</v>
+        <v>7.941375</v>
       </c>
       <c r="N26">
-        <v>48.97628</v>
+        <v>48.65862499999999</v>
       </c>
       <c r="O26">
-        <v>12.24407</v>
+        <v>12.16465625</v>
       </c>
       <c r="P26">
-        <v>36.73220999999999</v>
+        <v>36.49396874999999</v>
       </c>
       <c r="Q26">
-        <v>58.73220999999999</v>
+        <v>58.49396874999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09096308698253509</v>
+        <v>0.09144354535468972</v>
       </c>
       <c r="T26">
-        <v>0.6986585920369711</v>
+        <v>0.7060911302501304</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.424197111121604</v>
+        <v>7.127229226676739</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07876390901601729</v>
+        <v>0.07862187192530791</v>
       </c>
       <c r="C27">
-        <v>481.5080981670707</v>
+        <v>477.8067245269848</v>
       </c>
       <c r="D27">
-        <v>591.7580981670707</v>
+        <v>593.9067245269848</v>
       </c>
       <c r="E27">
-        <v>77.65000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="F27">
-        <v>146.25</v>
+        <v>152.1</v>
       </c>
       <c r="G27">
         <v>36</v>
@@ -3501,28 +3501,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M27">
-        <v>7.941375</v>
+        <v>8.259029999999999</v>
       </c>
       <c r="N27">
-        <v>48.65862499999999</v>
+        <v>48.34097</v>
       </c>
       <c r="O27">
-        <v>12.16465625</v>
+        <v>12.0852425</v>
       </c>
       <c r="P27">
-        <v>36.49396874999999</v>
+        <v>36.2557275</v>
       </c>
       <c r="Q27">
-        <v>58.49396874999999</v>
+        <v>58.2557275</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09144354535468972</v>
+        <v>0.09193698908825393</v>
       </c>
       <c r="T27">
-        <v>0.7060911302501304</v>
+        <v>0.7137245478744562</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.127229226676739</v>
+        <v>6.853105025650712</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07862187192530791</v>
+        <v>0.07847983483459853</v>
       </c>
       <c r="C28">
-        <v>477.8067245269848</v>
+        <v>474.1210107277096</v>
       </c>
       <c r="D28">
-        <v>593.9067245269848</v>
+        <v>596.0710107277097</v>
       </c>
       <c r="E28">
-        <v>83.5</v>
+        <v>89.35000000000002</v>
       </c>
       <c r="F28">
-        <v>152.1</v>
+        <v>157.95</v>
       </c>
       <c r="G28">
         <v>36</v>
@@ -3583,28 +3583,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M28">
-        <v>8.259029999999999</v>
+        <v>8.576685000000001</v>
       </c>
       <c r="N28">
-        <v>48.34097</v>
+        <v>48.023315</v>
       </c>
       <c r="O28">
-        <v>12.0852425</v>
+        <v>12.00582875</v>
       </c>
       <c r="P28">
-        <v>36.2557275</v>
+        <v>36.01748625</v>
       </c>
       <c r="Q28">
-        <v>58.2557275</v>
+        <v>58.01748625</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09193698908825393</v>
+        <v>0.09244395182821717</v>
       </c>
       <c r="T28">
-        <v>0.7137245478744562</v>
+        <v>0.7215671002282155</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.853105025650712</v>
+        <v>6.59928632099698</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07847983483459853</v>
+        <v>0.07833779774388915</v>
       </c>
       <c r="C29">
-        <v>474.1210107277096</v>
+        <v>470.4511285959146</v>
       </c>
       <c r="D29">
-        <v>596.0710107277097</v>
+        <v>598.2511285959146</v>
       </c>
       <c r="E29">
-        <v>89.35000000000002</v>
+        <v>95.20000000000002</v>
       </c>
       <c r="F29">
-        <v>157.95</v>
+        <v>163.8</v>
       </c>
       <c r="G29">
         <v>36</v>
@@ -3665,28 +3665,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M29">
-        <v>8.576685000000001</v>
+        <v>8.894340000000001</v>
       </c>
       <c r="N29">
-        <v>48.023315</v>
+        <v>47.70565999999999</v>
       </c>
       <c r="O29">
-        <v>12.00582875</v>
+        <v>11.926415</v>
       </c>
       <c r="P29">
-        <v>36.01748625</v>
+        <v>35.779245</v>
       </c>
       <c r="Q29">
-        <v>58.01748625</v>
+        <v>57.779245</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09244395182821717</v>
+        <v>0.09296499686651272</v>
       </c>
       <c r="T29">
-        <v>0.7215671002282155</v>
+        <v>0.7296275012584681</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.59928632099698</v>
+        <v>6.363597523818517</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07833779774388915</v>
+        <v>0.07819576065317976</v>
       </c>
       <c r="C30">
-        <v>470.4511285959146</v>
+        <v>466.7972524813065</v>
       </c>
       <c r="D30">
-        <v>598.2511285959146</v>
+        <v>600.4472524813066</v>
       </c>
       <c r="E30">
-        <v>95.20000000000002</v>
+        <v>101.05</v>
       </c>
       <c r="F30">
-        <v>163.8</v>
+        <v>169.65</v>
       </c>
       <c r="G30">
         <v>36</v>
@@ -3747,28 +3747,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M30">
-        <v>8.894340000000001</v>
+        <v>9.211995000000002</v>
       </c>
       <c r="N30">
-        <v>47.70565999999999</v>
+        <v>47.38800499999999</v>
       </c>
       <c r="O30">
-        <v>11.926415</v>
+        <v>11.84700125</v>
       </c>
       <c r="P30">
-        <v>35.779245</v>
+        <v>35.54100374999999</v>
       </c>
       <c r="Q30">
-        <v>57.779245</v>
+        <v>57.54100374999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09296499686651272</v>
+        <v>0.09350071922983066</v>
       </c>
       <c r="T30">
-        <v>0.7296275012584681</v>
+        <v>0.7379149558388686</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.363597523818517</v>
+        <v>6.144163126445465</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07819576065317976</v>
+        <v>0.07827872356247037</v>
       </c>
       <c r="C31">
-        <v>466.7972524813066</v>
+        <v>459.6625570508768</v>
       </c>
       <c r="D31">
-        <v>600.4472524813066</v>
+        <v>599.1625570508768</v>
       </c>
       <c r="E31">
-        <v>101.05</v>
+        <v>106.9</v>
       </c>
       <c r="F31">
-        <v>169.65</v>
+        <v>175.5</v>
       </c>
       <c r="G31">
         <v>36</v>
@@ -3829,45 +3829,45 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M31">
-        <v>9.211994999999998</v>
+        <v>9.70515</v>
       </c>
       <c r="N31">
-        <v>47.38800499999999</v>
+        <v>46.89484999999999</v>
       </c>
       <c r="O31">
-        <v>11.84700125</v>
+        <v>11.7237125</v>
       </c>
       <c r="P31">
-        <v>35.54100374999999</v>
+        <v>35.17113749999999</v>
       </c>
       <c r="Q31">
-        <v>57.54100374999999</v>
+        <v>57.17113749999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09350071922983066</v>
+        <v>0.09405174794638627</v>
       </c>
       <c r="T31">
-        <v>0.7379149558388686</v>
+        <v>0.7464391948358521</v>
       </c>
       <c r="U31">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V31">
         <v>0.25</v>
       </c>
       <c r="W31">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>6.144163126445466</v>
+        <v>5.831955199043806</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07827872356247037</v>
+        <v>0.07814418647176101</v>
       </c>
       <c r="C32">
-        <v>459.6625570508768</v>
+        <v>455.8986684870282</v>
       </c>
       <c r="D32">
-        <v>599.1625570508768</v>
+        <v>601.2486684870282</v>
       </c>
       <c r="E32">
-        <v>106.9</v>
+        <v>112.75</v>
       </c>
       <c r="F32">
-        <v>175.5</v>
+        <v>181.35</v>
       </c>
       <c r="G32">
         <v>36</v>
@@ -3911,28 +3911,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M32">
-        <v>9.70515</v>
+        <v>10.028655</v>
       </c>
       <c r="N32">
-        <v>46.89484999999999</v>
+        <v>46.57134499999999</v>
       </c>
       <c r="O32">
-        <v>11.7237125</v>
+        <v>11.64283625</v>
       </c>
       <c r="P32">
-        <v>35.17113749999999</v>
+        <v>34.92850874999999</v>
       </c>
       <c r="Q32">
-        <v>57.17113749999999</v>
+        <v>56.92850874999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09405174794638627</v>
+        <v>0.09461874850979857</v>
       </c>
       <c r="T32">
-        <v>0.7464391948358521</v>
+        <v>0.7552105132240524</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.831955199043806</v>
+        <v>5.643827611977876</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07814418647176101</v>
+        <v>0.07800964938105162</v>
       </c>
       <c r="C33">
-        <v>455.8986684870282</v>
+        <v>452.149357155144</v>
       </c>
       <c r="D33">
-        <v>601.2486684870282</v>
+        <v>603.349357155144</v>
       </c>
       <c r="E33">
-        <v>112.75</v>
+        <v>118.6</v>
       </c>
       <c r="F33">
-        <v>181.35</v>
+        <v>187.2</v>
       </c>
       <c r="G33">
         <v>36</v>
@@ -3993,28 +3993,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M33">
-        <v>10.028655</v>
+        <v>10.35216</v>
       </c>
       <c r="N33">
-        <v>46.57134499999999</v>
+        <v>46.24784</v>
       </c>
       <c r="O33">
-        <v>11.64283625</v>
+        <v>11.56196</v>
       </c>
       <c r="P33">
-        <v>34.92850874999999</v>
+        <v>34.68588</v>
       </c>
       <c r="Q33">
-        <v>56.92850874999999</v>
+        <v>56.68588</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09461874850979857</v>
+        <v>0.09520242556037005</v>
       </c>
       <c r="T33">
-        <v>0.7552105132240524</v>
+        <v>0.764239811564847</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.643827611977876</v>
+        <v>5.467457999103567</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07800964938105162</v>
+        <v>0.07787511229034225</v>
       </c>
       <c r="C34">
-        <v>452.149357155144</v>
+        <v>448.4147763840862</v>
       </c>
       <c r="D34">
-        <v>603.349357155144</v>
+        <v>605.4647763840862</v>
       </c>
       <c r="E34">
-        <v>118.6</v>
+        <v>124.45</v>
       </c>
       <c r="F34">
-        <v>187.2</v>
+        <v>193.05</v>
       </c>
       <c r="G34">
         <v>36</v>
@@ -4075,28 +4075,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M34">
-        <v>10.35216</v>
+        <v>10.675665</v>
       </c>
       <c r="N34">
-        <v>46.24784</v>
+        <v>45.92433499999999</v>
       </c>
       <c r="O34">
-        <v>11.56196</v>
+        <v>11.48108375</v>
       </c>
       <c r="P34">
-        <v>34.68588</v>
+        <v>34.44325125</v>
       </c>
       <c r="Q34">
-        <v>56.68588</v>
+        <v>56.44325125</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09520242556037005</v>
+        <v>0.09580352580648098</v>
       </c>
       <c r="T34">
-        <v>0.764239811564847</v>
+        <v>0.7735386411993966</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.467457999103567</v>
+        <v>5.301777453676187</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07787511229034225</v>
+        <v>0.07774057519963287</v>
       </c>
       <c r="C35">
-        <v>448.4147763840862</v>
+        <v>444.6950816606443</v>
       </c>
       <c r="D35">
-        <v>605.4647763840862</v>
+        <v>607.5950816606443</v>
       </c>
       <c r="E35">
-        <v>124.45</v>
+        <v>130.3</v>
       </c>
       <c r="F35">
-        <v>193.05</v>
+        <v>198.9</v>
       </c>
       <c r="G35">
         <v>36</v>
@@ -4157,28 +4157,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M35">
-        <v>10.675665</v>
+        <v>10.99917</v>
       </c>
       <c r="N35">
-        <v>45.92433499999999</v>
+        <v>45.60082999999999</v>
       </c>
       <c r="O35">
-        <v>11.48108375</v>
+        <v>11.4002075</v>
       </c>
       <c r="P35">
-        <v>34.44325125</v>
+        <v>34.20062249999999</v>
       </c>
       <c r="Q35">
-        <v>56.44325125</v>
+        <v>56.20062249999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09580352580648098</v>
+        <v>0.09642284121156497</v>
       </c>
       <c r="T35">
-        <v>0.7735386411993966</v>
+        <v>0.7831192535501447</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.301777453676187</v>
+        <v>5.145842822685711</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07774057519963287</v>
+        <v>0.0776060381089235</v>
       </c>
       <c r="C36">
-        <v>444.6950816606443</v>
+        <v>440.9904306676328</v>
       </c>
       <c r="D36">
-        <v>607.5950816606443</v>
+        <v>609.7404306676328</v>
       </c>
       <c r="E36">
-        <v>130.3</v>
+        <v>136.15</v>
       </c>
       <c r="F36">
-        <v>198.9</v>
+        <v>204.75</v>
       </c>
       <c r="G36">
         <v>36</v>
@@ -4239,28 +4239,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M36">
-        <v>10.99917</v>
+        <v>11.322675</v>
       </c>
       <c r="N36">
-        <v>45.60082999999999</v>
+        <v>45.27732499999999</v>
       </c>
       <c r="O36">
-        <v>11.4002075</v>
+        <v>11.31933125</v>
       </c>
       <c r="P36">
-        <v>34.20062249999999</v>
+        <v>33.95799374999999</v>
       </c>
       <c r="Q36">
-        <v>56.20062249999999</v>
+        <v>55.95799374999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09642284121156497</v>
+        <v>0.09706121247526692</v>
       </c>
       <c r="T36">
-        <v>0.7831192535501447</v>
+        <v>0.7929946539732233</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.145842822685711</v>
+        <v>4.998818742037547</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0776060381089235</v>
+        <v>0.07747150101821411</v>
       </c>
       <c r="C37">
-        <v>440.9904306676328</v>
+        <v>437.3009833227975</v>
       </c>
       <c r="D37">
-        <v>609.7404306676328</v>
+        <v>611.9009833227975</v>
       </c>
       <c r="E37">
-        <v>136.15</v>
+        <v>142</v>
       </c>
       <c r="F37">
-        <v>204.75</v>
+        <v>210.6</v>
       </c>
       <c r="G37">
         <v>36</v>
@@ -4321,28 +4321,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M37">
-        <v>11.322675</v>
+        <v>11.64618</v>
       </c>
       <c r="N37">
-        <v>45.27732499999999</v>
+        <v>44.95381999999999</v>
       </c>
       <c r="O37">
-        <v>11.31933125</v>
+        <v>11.238455</v>
       </c>
       <c r="P37">
-        <v>33.95799374999999</v>
+        <v>33.71536499999999</v>
       </c>
       <c r="Q37">
-        <v>55.95799374999999</v>
+        <v>55.71536499999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09706121247526692</v>
+        <v>0.09771953284095955</v>
       </c>
       <c r="T37">
-        <v>0.7929946539732233</v>
+        <v>0.8031786606595233</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.998818742037547</v>
+        <v>4.859962665869838</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07747150101821411</v>
+        <v>0.07733696392750473</v>
       </c>
       <c r="C38">
-        <v>437.3009833227975</v>
+        <v>433.6269018185525</v>
       </c>
       <c r="D38">
-        <v>611.9009833227975</v>
+        <v>614.0769018185525</v>
       </c>
       <c r="E38">
-        <v>142</v>
+        <v>147.85</v>
       </c>
       <c r="F38">
-        <v>210.6</v>
+        <v>216.45</v>
       </c>
       <c r="G38">
         <v>36</v>
@@ -4403,28 +4403,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M38">
-        <v>11.64618</v>
+        <v>11.969685</v>
       </c>
       <c r="N38">
-        <v>44.95381999999999</v>
+        <v>44.630315</v>
       </c>
       <c r="O38">
-        <v>11.238455</v>
+        <v>11.15757875</v>
       </c>
       <c r="P38">
-        <v>33.71536499999999</v>
+        <v>33.47273625</v>
       </c>
       <c r="Q38">
-        <v>55.71536499999999</v>
+        <v>55.47273625</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09771953284095955</v>
+        <v>0.09839875226588053</v>
       </c>
       <c r="T38">
-        <v>0.8031786606595233</v>
+        <v>0.8136859691453883</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.859962665869839</v>
+        <v>4.728612323549032</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07733696392750473</v>
+        <v>0.07720242683679536</v>
       </c>
       <c r="C39">
-        <v>433.6269018185525</v>
+        <v>429.9683506625685</v>
       </c>
       <c r="D39">
-        <v>614.0769018185525</v>
+        <v>616.2683506625685</v>
       </c>
       <c r="E39">
-        <v>147.85</v>
+        <v>153.7</v>
       </c>
       <c r="F39">
-        <v>216.45</v>
+        <v>222.3</v>
       </c>
       <c r="G39">
         <v>36</v>
@@ -4485,28 +4485,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M39">
-        <v>11.969685</v>
+        <v>12.29319</v>
       </c>
       <c r="N39">
-        <v>44.630315</v>
+        <v>44.30680999999999</v>
       </c>
       <c r="O39">
-        <v>11.15757875</v>
+        <v>11.0767025</v>
       </c>
       <c r="P39">
-        <v>33.47273625</v>
+        <v>33.2301075</v>
       </c>
       <c r="Q39">
-        <v>55.47273625</v>
+        <v>55.2301075</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09839875226588053</v>
+        <v>0.09909988199483122</v>
       </c>
       <c r="T39">
-        <v>0.8136859691453883</v>
+        <v>0.8245322230662813</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.728612323549032</v>
+        <v>4.604175157139847</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07720242683679536</v>
+        <v>0.07779913974608597</v>
       </c>
       <c r="C40">
-        <v>429.9683506625685</v>
+        <v>414.5159113912607</v>
       </c>
       <c r="D40">
-        <v>616.2683506625685</v>
+        <v>606.6659113912607</v>
       </c>
       <c r="E40">
-        <v>153.7</v>
+        <v>159.55</v>
       </c>
       <c r="F40">
-        <v>222.3</v>
+        <v>228.15</v>
       </c>
       <c r="G40">
         <v>36</v>
@@ -4567,45 +4567,45 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M40">
-        <v>12.29319</v>
+        <v>13.18707</v>
       </c>
       <c r="N40">
-        <v>44.30680999999999</v>
+        <v>43.41292999999999</v>
       </c>
       <c r="O40">
-        <v>11.0767025</v>
+        <v>10.8532325</v>
       </c>
       <c r="P40">
-        <v>33.2301075</v>
+        <v>32.55969749999999</v>
       </c>
       <c r="Q40">
-        <v>55.2301075</v>
+        <v>54.55969749999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09909988199483122</v>
+        <v>0.09982399958374749</v>
       </c>
       <c r="T40">
-        <v>0.8245322230662813</v>
+        <v>0.8357340918698264</v>
       </c>
       <c r="U40">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V40">
         <v>0.25</v>
       </c>
       <c r="W40">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>4.604175157139847</v>
+        <v>4.292083078348714</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07779913974608597</v>
+        <v>0.0776833526553766</v>
       </c>
       <c r="C41">
-        <v>414.5159113912607</v>
+        <v>410.5057133351788</v>
       </c>
       <c r="D41">
-        <v>606.6659113912607</v>
+        <v>608.5057133351788</v>
       </c>
       <c r="E41">
-        <v>159.55</v>
+        <v>165.4</v>
       </c>
       <c r="F41">
-        <v>228.15</v>
+        <v>234</v>
       </c>
       <c r="G41">
         <v>36</v>
@@ -4649,28 +4649,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M41">
-        <v>13.18707</v>
+        <v>13.5252</v>
       </c>
       <c r="N41">
-        <v>43.41292999999999</v>
+        <v>43.0748</v>
       </c>
       <c r="O41">
-        <v>10.8532325</v>
+        <v>10.7687</v>
       </c>
       <c r="P41">
-        <v>32.55969749999999</v>
+        <v>32.3061</v>
       </c>
       <c r="Q41">
-        <v>54.55969749999999</v>
+        <v>54.3061</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09982399958374749</v>
+        <v>0.1005722544256277</v>
       </c>
       <c r="T41">
-        <v>0.8357340918698264</v>
+        <v>0.8473093563001564</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.292083078348714</v>
+        <v>4.184781001389997</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0776833526553766</v>
+        <v>0.07756756556466722</v>
       </c>
       <c r="C42">
-        <v>410.5057133351788</v>
+        <v>406.5067081530154</v>
       </c>
       <c r="D42">
-        <v>608.5057133351788</v>
+        <v>610.3567081530155</v>
       </c>
       <c r="E42">
-        <v>165.4</v>
+        <v>171.25</v>
       </c>
       <c r="F42">
-        <v>234</v>
+        <v>239.85</v>
       </c>
       <c r="G42">
         <v>36</v>
@@ -4731,28 +4731,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M42">
-        <v>13.5252</v>
+        <v>13.86333</v>
       </c>
       <c r="N42">
-        <v>43.0748</v>
+        <v>42.73666999999999</v>
       </c>
       <c r="O42">
-        <v>10.7687</v>
+        <v>10.6841675</v>
       </c>
       <c r="P42">
-        <v>32.3061</v>
+        <v>32.05250249999999</v>
       </c>
       <c r="Q42">
-        <v>54.3061</v>
+        <v>54.05250249999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1005722544256277</v>
+        <v>0.101345873838419</v>
       </c>
       <c r="T42">
-        <v>0.8473093563001564</v>
+        <v>0.8592770025755825</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.184781001389997</v>
+        <v>4.082713172087802</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07756756556466722</v>
+        <v>0.07855427847395784</v>
       </c>
       <c r="C43">
-        <v>406.5067081530154</v>
+        <v>385.2347144425637</v>
       </c>
       <c r="D43">
-        <v>610.3567081530155</v>
+        <v>594.9347144425637</v>
       </c>
       <c r="E43">
-        <v>171.25</v>
+        <v>177.1</v>
       </c>
       <c r="F43">
-        <v>239.85</v>
+        <v>245.7</v>
       </c>
       <c r="G43">
         <v>36</v>
@@ -4813,45 +4813,45 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M43">
-        <v>13.86333</v>
+        <v>15.06141</v>
       </c>
       <c r="N43">
-        <v>42.73666999999999</v>
+        <v>41.53858999999999</v>
       </c>
       <c r="O43">
-        <v>10.6841675</v>
+        <v>10.3846475</v>
       </c>
       <c r="P43">
-        <v>32.05250249999999</v>
+        <v>31.15394249999999</v>
       </c>
       <c r="Q43">
-        <v>54.05250249999999</v>
+        <v>53.15394249999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.101345873838419</v>
+        <v>0.1021461697826859</v>
       </c>
       <c r="T43">
-        <v>0.8592770025755825</v>
+        <v>0.8716573263087816</v>
       </c>
       <c r="U43">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V43">
         <v>0.25</v>
       </c>
       <c r="W43">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.082713172087802</v>
+        <v>3.757948293021702</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07855427847395785</v>
+        <v>0.07846474138324847</v>
       </c>
       <c r="C44">
-        <v>385.2347144425635</v>
+        <v>380.7519242945218</v>
       </c>
       <c r="D44">
-        <v>594.9347144425635</v>
+        <v>596.3019242945218</v>
       </c>
       <c r="E44">
-        <v>177.1</v>
+        <v>182.95</v>
       </c>
       <c r="F44">
-        <v>245.7</v>
+        <v>251.55</v>
       </c>
       <c r="G44">
         <v>36</v>
@@ -4895,28 +4895,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M44">
-        <v>15.06141</v>
+        <v>15.420015</v>
       </c>
       <c r="N44">
-        <v>41.53859</v>
+        <v>41.17998499999999</v>
       </c>
       <c r="O44">
-        <v>10.3846475</v>
+        <v>10.29499625</v>
       </c>
       <c r="P44">
-        <v>31.1539425</v>
+        <v>30.88498875</v>
       </c>
       <c r="Q44">
-        <v>53.1539425</v>
+        <v>52.88498875</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1021461697826859</v>
+        <v>0.1029745462864008</v>
       </c>
       <c r="T44">
-        <v>0.8716573263087816</v>
+        <v>0.8844720473659526</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.757948293021703</v>
+        <v>3.67055414667236</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07846474138324847</v>
+        <v>0.07837520429253909</v>
       </c>
       <c r="C45">
-        <v>380.7519242945218</v>
+        <v>376.275432546459</v>
       </c>
       <c r="D45">
-        <v>596.3019242945218</v>
+        <v>597.675432546459</v>
       </c>
       <c r="E45">
-        <v>182.95</v>
+        <v>188.8</v>
       </c>
       <c r="F45">
-        <v>251.55</v>
+        <v>257.4</v>
       </c>
       <c r="G45">
         <v>36</v>
@@ -4977,28 +4977,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M45">
-        <v>15.420015</v>
+        <v>15.77862</v>
       </c>
       <c r="N45">
-        <v>41.17998499999999</v>
+        <v>40.82138</v>
       </c>
       <c r="O45">
-        <v>10.29499625</v>
+        <v>10.205345</v>
       </c>
       <c r="P45">
-        <v>30.88498875</v>
+        <v>30.616035</v>
       </c>
       <c r="Q45">
-        <v>52.88498875</v>
+        <v>52.616035</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1029745462864008</v>
+        <v>0.1038325076652484</v>
       </c>
       <c r="T45">
-        <v>0.8844720473659526</v>
+        <v>0.8977444370323087</v>
       </c>
       <c r="U45">
         <v>0.0613</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.67055414667236</v>
+        <v>3.587132461520716</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07837520429253909</v>
+        <v>0.0782856672018297</v>
       </c>
       <c r="C46">
-        <v>376.275432546459</v>
+        <v>371.8052828216292</v>
       </c>
       <c r="D46">
-        <v>597.675432546459</v>
+        <v>599.0552828216292</v>
       </c>
       <c r="E46">
-        <v>188.8</v>
+        <v>194.65</v>
       </c>
       <c r="F46">
-        <v>257.4</v>
+        <v>263.25</v>
       </c>
       <c r="G46">
         <v>36</v>
@@ -5059,28 +5059,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M46">
-        <v>15.77862</v>
+        <v>16.137225</v>
       </c>
       <c r="N46">
-        <v>40.82138</v>
+        <v>40.46277499999999</v>
       </c>
       <c r="O46">
-        <v>10.205345</v>
+        <v>10.11569375</v>
       </c>
       <c r="P46">
-        <v>30.616035</v>
+        <v>30.34708125</v>
       </c>
       <c r="Q46">
-        <v>52.616035</v>
+        <v>52.34708125</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1038325076652484</v>
+        <v>0.1047216676396903</v>
       </c>
       <c r="T46">
-        <v>0.8977444370323087</v>
+        <v>0.9114994590501682</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.587132461520716</v>
+        <v>3.507418406820255</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0782856672018297</v>
+        <v>0.07916213011112033</v>
       </c>
       <c r="C47">
-        <v>371.8052828216292</v>
+        <v>352.7161820703042</v>
       </c>
       <c r="D47">
-        <v>599.0552828216292</v>
+        <v>585.8161820703042</v>
       </c>
       <c r="E47">
-        <v>194.65</v>
+        <v>200.5</v>
       </c>
       <c r="F47">
-        <v>263.25</v>
+        <v>269.1</v>
       </c>
       <c r="G47">
         <v>36</v>
@@ -5141,45 +5141,45 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M47">
-        <v>16.137225</v>
+        <v>17.24931</v>
       </c>
       <c r="N47">
-        <v>40.46277499999999</v>
+        <v>39.35068999999999</v>
       </c>
       <c r="O47">
-        <v>10.11569375</v>
+        <v>9.837672499999998</v>
       </c>
       <c r="P47">
-        <v>30.34708125</v>
+        <v>29.5130175</v>
       </c>
       <c r="Q47">
-        <v>52.34708125</v>
+        <v>51.5130175</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1047216676396903</v>
+        <v>0.1056437594650376</v>
       </c>
       <c r="T47">
-        <v>0.9114994590501682</v>
+        <v>0.9257639263279487</v>
       </c>
       <c r="U47">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V47">
         <v>0.25</v>
       </c>
       <c r="W47">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>3.507418406820255</v>
+        <v>3.281290671916731</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07916213011112033</v>
+        <v>0.07909359302041094</v>
       </c>
       <c r="C48">
-        <v>352.7161820703042</v>
+        <v>347.8803181911669</v>
       </c>
       <c r="D48">
-        <v>585.8161820703042</v>
+        <v>586.8303181911668</v>
       </c>
       <c r="E48">
-        <v>200.5</v>
+        <v>206.35</v>
       </c>
       <c r="F48">
-        <v>269.1</v>
+        <v>274.95</v>
       </c>
       <c r="G48">
         <v>36</v>
@@ -5223,28 +5223,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M48">
-        <v>17.24931</v>
+        <v>17.624295</v>
       </c>
       <c r="N48">
-        <v>39.35068999999999</v>
+        <v>38.97570499999999</v>
       </c>
       <c r="O48">
-        <v>9.837672499999998</v>
+        <v>9.743926249999998</v>
       </c>
       <c r="P48">
-        <v>29.5130175</v>
+        <v>29.23177874999999</v>
       </c>
       <c r="Q48">
-        <v>51.5130175</v>
+        <v>51.23177874999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1056437594650376</v>
+        <v>0.1066006472083225</v>
       </c>
       <c r="T48">
-        <v>0.9257639263279487</v>
+        <v>0.9405666753897962</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.281290671916731</v>
+        <v>3.211475976769567</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07909359302041094</v>
+        <v>0.07902505592970158</v>
       </c>
       <c r="C49">
-        <v>347.8803181911669</v>
+        <v>343.0479716460696</v>
       </c>
       <c r="D49">
-        <v>586.8303181911668</v>
+        <v>587.8479716460696</v>
       </c>
       <c r="E49">
-        <v>206.35</v>
+        <v>212.2</v>
       </c>
       <c r="F49">
-        <v>274.95</v>
+        <v>280.8</v>
       </c>
       <c r="G49">
         <v>36</v>
@@ -5305,28 +5305,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M49">
-        <v>17.624295</v>
+        <v>17.99928</v>
       </c>
       <c r="N49">
-        <v>38.97570499999999</v>
+        <v>38.60072</v>
       </c>
       <c r="O49">
-        <v>9.743926249999998</v>
+        <v>9.650179999999999</v>
       </c>
       <c r="P49">
-        <v>29.23177874999999</v>
+        <v>28.95054</v>
       </c>
       <c r="Q49">
-        <v>51.23177874999999</v>
+        <v>50.95054</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1066006472083225</v>
+        <v>0.1075943383263492</v>
       </c>
       <c r="T49">
-        <v>0.9405666753897962</v>
+        <v>0.9559387609540226</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.211475976769567</v>
+        <v>3.144570227253534</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07902505592970156</v>
+        <v>0.07895651883899218</v>
       </c>
       <c r="C50">
-        <v>343.0479716460698</v>
+        <v>338.2191607655859</v>
       </c>
       <c r="D50">
-        <v>587.8479716460698</v>
+        <v>588.8691607655859</v>
       </c>
       <c r="E50">
-        <v>212.2</v>
+        <v>218.05</v>
       </c>
       <c r="F50">
-        <v>280.8</v>
+        <v>286.65</v>
       </c>
       <c r="G50">
         <v>36</v>
@@ -5387,28 +5387,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M50">
-        <v>17.99928</v>
+        <v>18.374265</v>
       </c>
       <c r="N50">
-        <v>38.60072</v>
+        <v>38.22573499999999</v>
       </c>
       <c r="O50">
-        <v>9.650179999999999</v>
+        <v>9.556433749999998</v>
       </c>
       <c r="P50">
-        <v>28.95054</v>
+        <v>28.66930125</v>
       </c>
       <c r="Q50">
-        <v>50.95054</v>
+        <v>50.66930125</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1075943383263492</v>
+        <v>0.1086269977235141</v>
       </c>
       <c r="T50">
-        <v>0.9559387609540226</v>
+        <v>0.9719136734031205</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.144570227253534</v>
+        <v>3.080395324656523</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07895651883899218</v>
+        <v>0.07888798174828281</v>
       </c>
       <c r="C51">
-        <v>338.2191607655859</v>
+        <v>333.3939040078818</v>
       </c>
       <c r="D51">
-        <v>588.8691607655859</v>
+        <v>589.8939040078818</v>
       </c>
       <c r="E51">
-        <v>218.05</v>
+        <v>223.9</v>
       </c>
       <c r="F51">
-        <v>286.65</v>
+        <v>292.5</v>
       </c>
       <c r="G51">
         <v>36</v>
@@ -5469,28 +5469,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M51">
-        <v>18.374265</v>
+        <v>18.74925</v>
       </c>
       <c r="N51">
-        <v>38.22573499999999</v>
+        <v>37.85074999999999</v>
       </c>
       <c r="O51">
-        <v>9.556433749999998</v>
+        <v>9.462687499999998</v>
       </c>
       <c r="P51">
-        <v>28.66930125</v>
+        <v>28.38806249999999</v>
       </c>
       <c r="Q51">
-        <v>50.66930125</v>
+        <v>50.38806249999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1086269977235141</v>
+        <v>0.1097009634965656</v>
       </c>
       <c r="T51">
-        <v>0.9719136734031205</v>
+        <v>0.9885275823501825</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.080395324656523</v>
+        <v>3.018787418163393</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07888798174828281</v>
+        <v>0.08180294465757343</v>
       </c>
       <c r="C52">
-        <v>333.3939040078818</v>
+        <v>286.8931793124879</v>
       </c>
       <c r="D52">
-        <v>589.8939040078818</v>
+        <v>549.2431793124879</v>
       </c>
       <c r="E52">
-        <v>223.9</v>
+        <v>229.75</v>
       </c>
       <c r="F52">
-        <v>292.5</v>
+        <v>298.35</v>
       </c>
       <c r="G52">
         <v>36</v>
@@ -5551,45 +5551,45 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M52">
-        <v>18.74925</v>
+        <v>21.451365</v>
       </c>
       <c r="N52">
-        <v>37.85074999999999</v>
+        <v>35.14863499999999</v>
       </c>
       <c r="O52">
-        <v>9.462687499999998</v>
+        <v>8.787158749999998</v>
       </c>
       <c r="P52">
-        <v>28.38806249999999</v>
+        <v>26.36147625</v>
       </c>
       <c r="Q52">
-        <v>50.38806249999999</v>
+        <v>48.36147625</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1097009634965656</v>
+        <v>0.1108187646072927</v>
       </c>
       <c r="T52">
-        <v>0.9885275823501825</v>
+        <v>1.005819610029778</v>
       </c>
       <c r="U52">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V52">
         <v>0.25</v>
       </c>
       <c r="W52">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>3.018787418163393</v>
+        <v>2.638526732448028</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08180294465757343</v>
+        <v>0.08179290756686404</v>
       </c>
       <c r="C53">
-        <v>286.8931793124879</v>
+        <v>281.1735370865786</v>
       </c>
       <c r="D53">
-        <v>549.2431793124879</v>
+        <v>549.3735370865786</v>
       </c>
       <c r="E53">
-        <v>229.75</v>
+        <v>235.6</v>
       </c>
       <c r="F53">
-        <v>298.35</v>
+        <v>304.2</v>
       </c>
       <c r="G53">
         <v>36</v>
@@ -5633,28 +5633,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M53">
-        <v>21.451365</v>
+        <v>21.87198</v>
       </c>
       <c r="N53">
-        <v>35.14863499999999</v>
+        <v>34.72801999999999</v>
       </c>
       <c r="O53">
-        <v>8.787158749999998</v>
+        <v>8.682004999999998</v>
       </c>
       <c r="P53">
-        <v>26.36147625</v>
+        <v>26.046015</v>
       </c>
       <c r="Q53">
-        <v>48.36147625</v>
+        <v>48.046015</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1108187646072927</v>
+        <v>0.1119831407643001</v>
       </c>
       <c r="T53">
-        <v>1.005819610029778</v>
+        <v>1.023832138862689</v>
       </c>
       <c r="U53">
         <v>0.07190000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.638526732448028</v>
+        <v>2.587785833747104</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08179290756686404</v>
+        <v>0.08178287047615468</v>
       </c>
       <c r="C54">
-        <v>281.1735370865786</v>
+        <v>275.4539567537755</v>
       </c>
       <c r="D54">
-        <v>549.3735370865786</v>
+        <v>549.5039567537755</v>
       </c>
       <c r="E54">
-        <v>235.6</v>
+        <v>241.45</v>
       </c>
       <c r="F54">
-        <v>304.2</v>
+        <v>310.05</v>
       </c>
       <c r="G54">
         <v>36</v>
@@ -5715,28 +5715,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M54">
-        <v>21.87198</v>
+        <v>22.292595</v>
       </c>
       <c r="N54">
-        <v>34.72801999999999</v>
+        <v>34.30740499999999</v>
       </c>
       <c r="O54">
-        <v>8.682004999999998</v>
+        <v>8.576851249999997</v>
       </c>
       <c r="P54">
-        <v>26.046015</v>
+        <v>25.73055374999999</v>
       </c>
       <c r="Q54">
-        <v>48.046015</v>
+        <v>47.73055374999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1119831407643001</v>
+        <v>0.1131970648428823</v>
       </c>
       <c r="T54">
-        <v>1.023832138862689</v>
+        <v>1.042611158284235</v>
       </c>
       <c r="U54">
         <v>0.07190000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.587785833747104</v>
+        <v>2.538959685940555</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08178287047615468</v>
+        <v>0.08335233338544529</v>
       </c>
       <c r="C55">
-        <v>275.4539567537755</v>
+        <v>249.9359660329865</v>
       </c>
       <c r="D55">
-        <v>549.5039567537755</v>
+        <v>529.8359660329866</v>
       </c>
       <c r="E55">
-        <v>241.45</v>
+        <v>247.3</v>
       </c>
       <c r="F55">
-        <v>310.05</v>
+        <v>315.9</v>
       </c>
       <c r="G55">
         <v>36</v>
@@ -5797,45 +5797,45 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M55">
-        <v>22.292595</v>
+        <v>23.94522000000001</v>
       </c>
       <c r="N55">
-        <v>34.30740499999999</v>
+        <v>32.65477999999999</v>
       </c>
       <c r="O55">
-        <v>8.576851249999997</v>
+        <v>8.163694999999997</v>
       </c>
       <c r="P55">
-        <v>25.73055374999999</v>
+        <v>24.49108499999999</v>
       </c>
       <c r="Q55">
-        <v>47.73055374999999</v>
+        <v>46.49108499999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1131970648428823</v>
+        <v>0.1144637682292289</v>
       </c>
       <c r="T55">
-        <v>1.042611158284235</v>
+        <v>1.062206656811066</v>
       </c>
       <c r="U55">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V55">
         <v>0.25</v>
       </c>
       <c r="W55">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.538959685940555</v>
+        <v>2.363728543734406</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08335233338544529</v>
+        <v>0.08337154629473591</v>
       </c>
       <c r="C56">
-        <v>249.9359660329865</v>
+        <v>243.8539155728758</v>
       </c>
       <c r="D56">
-        <v>529.8359660329866</v>
+        <v>529.6039155728758</v>
       </c>
       <c r="E56">
-        <v>247.3</v>
+        <v>253.15</v>
       </c>
       <c r="F56">
-        <v>315.9</v>
+        <v>321.75</v>
       </c>
       <c r="G56">
         <v>36</v>
@@ -5879,28 +5879,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M56">
-        <v>23.94522000000001</v>
+        <v>24.38865</v>
       </c>
       <c r="N56">
-        <v>32.65477999999999</v>
+        <v>32.21135</v>
       </c>
       <c r="O56">
-        <v>8.163694999999997</v>
+        <v>8.052837499999999</v>
       </c>
       <c r="P56">
-        <v>24.49108499999999</v>
+        <v>24.1585125</v>
       </c>
       <c r="Q56">
-        <v>46.49108499999999</v>
+        <v>46.1585125</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1144637682292289</v>
+        <v>0.1157867695438576</v>
       </c>
       <c r="T56">
-        <v>1.062206656811066</v>
+        <v>1.082673066383533</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.363728543734406</v>
+        <v>2.320751661121054</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08337154629473591</v>
+        <v>0.08339075920402653</v>
       </c>
       <c r="C57">
-        <v>243.8539155728758</v>
+        <v>237.7720682844878</v>
       </c>
       <c r="D57">
-        <v>529.6039155728758</v>
+        <v>529.3720682844878</v>
       </c>
       <c r="E57">
-        <v>253.15</v>
+        <v>259</v>
       </c>
       <c r="F57">
-        <v>321.75</v>
+        <v>327.6</v>
       </c>
       <c r="G57">
         <v>36</v>
@@ -5961,28 +5961,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M57">
-        <v>24.38865</v>
+        <v>24.83208</v>
       </c>
       <c r="N57">
-        <v>32.21135</v>
+        <v>31.76791999999999</v>
       </c>
       <c r="O57">
-        <v>8.052837499999999</v>
+        <v>7.941979999999997</v>
       </c>
       <c r="P57">
-        <v>24.1585125</v>
+        <v>23.82593999999999</v>
       </c>
       <c r="Q57">
-        <v>46.1585125</v>
+        <v>45.82593999999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1157867695438576</v>
+        <v>0.1171699072818785</v>
       </c>
       <c r="T57">
-        <v>1.082673066383533</v>
+        <v>1.104069767300204</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.320751661121054</v>
+        <v>2.279309667172464</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08339075920402653</v>
+        <v>0.08340997211331715</v>
       </c>
       <c r="C58">
-        <v>237.7720682844878</v>
+        <v>231.6904239011088</v>
       </c>
       <c r="D58">
-        <v>529.3720682844878</v>
+        <v>529.1404239011089</v>
       </c>
       <c r="E58">
-        <v>259</v>
+        <v>264.85</v>
       </c>
       <c r="F58">
-        <v>327.6</v>
+        <v>333.45</v>
       </c>
       <c r="G58">
         <v>36</v>
@@ -6043,28 +6043,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M58">
-        <v>24.83208</v>
+        <v>25.27551</v>
       </c>
       <c r="N58">
-        <v>31.76791999999999</v>
+        <v>31.32448999999999</v>
       </c>
       <c r="O58">
-        <v>7.941979999999997</v>
+        <v>7.831122499999998</v>
       </c>
       <c r="P58">
-        <v>23.82593999999999</v>
+        <v>23.49336749999999</v>
       </c>
       <c r="Q58">
-        <v>45.82593999999999</v>
+        <v>45.49336749999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1171699072818785</v>
+        <v>0.1186173770077143</v>
       </c>
       <c r="T58">
-        <v>1.104069767300204</v>
+        <v>1.126461663608348</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.279309667172464</v>
+        <v>2.239321778274701</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08340997211331715</v>
+        <v>0.08342918502260777</v>
       </c>
       <c r="C59">
-        <v>231.6904239011088</v>
+        <v>225.6089821564918</v>
       </c>
       <c r="D59">
-        <v>529.1404239011089</v>
+        <v>528.9089821564919</v>
       </c>
       <c r="E59">
-        <v>264.85</v>
+        <v>270.7</v>
       </c>
       <c r="F59">
-        <v>333.45</v>
+        <v>339.3000000000001</v>
       </c>
       <c r="G59">
         <v>36</v>
@@ -6125,28 +6125,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M59">
-        <v>25.27551</v>
+        <v>25.71894000000001</v>
       </c>
       <c r="N59">
-        <v>31.32448999999999</v>
+        <v>30.88105999999999</v>
       </c>
       <c r="O59">
-        <v>7.831122499999998</v>
+        <v>7.720264999999997</v>
       </c>
       <c r="P59">
-        <v>23.49336749999999</v>
+        <v>23.16079499999999</v>
       </c>
       <c r="Q59">
-        <v>45.49336749999999</v>
+        <v>45.16079499999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1186173770077143</v>
+        <v>0.1201337738633518</v>
       </c>
       <c r="T59">
-        <v>1.126461663608348</v>
+        <v>1.14991984069307</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.239321778274701</v>
+        <v>2.200712782097551</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08342918502260777</v>
+        <v>0.08344839793189839</v>
       </c>
       <c r="C60">
-        <v>225.6089821564919</v>
+        <v>219.5277427848556</v>
       </c>
       <c r="D60">
-        <v>528.9089821564919</v>
+        <v>528.6777427848556</v>
       </c>
       <c r="E60">
-        <v>270.6999999999999</v>
+        <v>276.55</v>
       </c>
       <c r="F60">
-        <v>339.3</v>
+        <v>345.15</v>
       </c>
       <c r="G60">
         <v>36</v>
@@ -6207,28 +6207,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M60">
-        <v>25.71894</v>
+        <v>26.16237</v>
       </c>
       <c r="N60">
-        <v>30.88105999999999</v>
+        <v>30.43763</v>
       </c>
       <c r="O60">
-        <v>7.720264999999999</v>
+        <v>7.609407499999999</v>
       </c>
       <c r="P60">
-        <v>23.160795</v>
+        <v>22.8282225</v>
       </c>
       <c r="Q60">
-        <v>45.16079499999999</v>
+        <v>44.8282225</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1201337738633518</v>
+        <v>0.1217241412973131</v>
       </c>
       <c r="T60">
-        <v>1.149919840693069</v>
+        <v>1.174522319098997</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.200712782097551</v>
+        <v>2.16341256545183</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08344839793189839</v>
+        <v>0.083467610841189</v>
       </c>
       <c r="C61">
-        <v>219.5277427848556</v>
+        <v>213.446705520883</v>
       </c>
       <c r="D61">
-        <v>528.6777427848556</v>
+        <v>528.446705520883</v>
       </c>
       <c r="E61">
-        <v>276.55</v>
+        <v>282.4</v>
       </c>
       <c r="F61">
-        <v>345.15</v>
+        <v>351</v>
       </c>
       <c r="G61">
         <v>36</v>
@@ -6289,28 +6289,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M61">
-        <v>26.16237</v>
+        <v>26.6058</v>
       </c>
       <c r="N61">
-        <v>30.43763</v>
+        <v>29.99419999999999</v>
       </c>
       <c r="O61">
-        <v>7.609407499999999</v>
+        <v>7.498549999999998</v>
       </c>
       <c r="P61">
-        <v>22.8282225</v>
+        <v>22.49564999999999</v>
       </c>
       <c r="Q61">
-        <v>44.8282225</v>
+        <v>44.49565</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1217241412973131</v>
+        <v>0.1233940271029725</v>
       </c>
       <c r="T61">
-        <v>1.174522319098997</v>
+        <v>1.200354921425222</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.16341256545183</v>
+        <v>2.127355689360966</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.083467610841189</v>
+        <v>0.08348682375047964</v>
       </c>
       <c r="C62">
-        <v>213.446705520883</v>
+        <v>207.3658700997209</v>
       </c>
       <c r="D62">
-        <v>528.446705520883</v>
+        <v>528.2158700997209</v>
       </c>
       <c r="E62">
-        <v>282.4</v>
+        <v>288.25</v>
       </c>
       <c r="F62">
-        <v>351</v>
+        <v>356.85</v>
       </c>
       <c r="G62">
         <v>36</v>
@@ -6371,28 +6371,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M62">
-        <v>26.6058</v>
+        <v>27.04923</v>
       </c>
       <c r="N62">
-        <v>29.99419999999999</v>
+        <v>29.55077</v>
       </c>
       <c r="O62">
-        <v>7.498549999999998</v>
+        <v>7.387692499999999</v>
       </c>
       <c r="P62">
-        <v>22.49564999999999</v>
+        <v>22.1630775</v>
       </c>
       <c r="Q62">
-        <v>44.49565</v>
+        <v>44.1630775</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1233940271029725</v>
+        <v>0.1251495480781529</v>
       </c>
       <c r="T62">
-        <v>1.200354921425222</v>
+        <v>1.227512272588688</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.127355689360966</v>
+        <v>2.092481005928819</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08348682375047964</v>
+        <v>0.08350603665977024</v>
       </c>
       <c r="C63">
-        <v>207.3658700997209</v>
+        <v>201.285236256979</v>
       </c>
       <c r="D63">
-        <v>528.2158700997209</v>
+        <v>527.985236256979</v>
       </c>
       <c r="E63">
-        <v>288.25</v>
+        <v>294.1</v>
       </c>
       <c r="F63">
-        <v>356.85</v>
+        <v>362.7</v>
       </c>
       <c r="G63">
         <v>36</v>
@@ -6453,28 +6453,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M63">
-        <v>27.04923</v>
+        <v>27.49266</v>
       </c>
       <c r="N63">
-        <v>29.55077</v>
+        <v>29.10733999999999</v>
       </c>
       <c r="O63">
-        <v>7.387692499999999</v>
+        <v>7.276834999999998</v>
       </c>
       <c r="P63">
-        <v>22.1630775</v>
+        <v>21.830505</v>
       </c>
       <c r="Q63">
-        <v>44.1630775</v>
+        <v>43.830505</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1251495480781529</v>
+        <v>0.1269974648941322</v>
       </c>
       <c r="T63">
-        <v>1.227512272588688</v>
+        <v>1.256098958023916</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.092481005928819</v>
+        <v>2.058731312284806</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08350603665977024</v>
+        <v>0.08352524956906088</v>
       </c>
       <c r="C64">
-        <v>201.285236256979</v>
+        <v>195.2048037287274</v>
       </c>
       <c r="D64">
-        <v>527.985236256979</v>
+        <v>527.7548037287274</v>
       </c>
       <c r="E64">
-        <v>294.1</v>
+        <v>299.95</v>
       </c>
       <c r="F64">
-        <v>362.7</v>
+        <v>368.55</v>
       </c>
       <c r="G64">
         <v>36</v>
@@ -6535,28 +6535,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M64">
-        <v>27.49266</v>
+        <v>27.93609</v>
       </c>
       <c r="N64">
-        <v>29.10733999999999</v>
+        <v>28.66390999999999</v>
       </c>
       <c r="O64">
-        <v>7.276834999999998</v>
+        <v>7.165977499999998</v>
       </c>
       <c r="P64">
-        <v>21.830505</v>
+        <v>21.49793249999999</v>
       </c>
       <c r="Q64">
-        <v>43.830505</v>
+        <v>43.49793249999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1269974648941322</v>
+        <v>0.1289452691055699</v>
       </c>
       <c r="T64">
-        <v>1.256098958023916</v>
+        <v>1.286230869698886</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.058731312284806</v>
+        <v>2.026053037486634</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08352524956906088</v>
+        <v>0.0903604624783515</v>
       </c>
       <c r="C65">
-        <v>195.2048037287274</v>
+        <v>118.4247136642035</v>
       </c>
       <c r="D65">
-        <v>527.7548037287274</v>
+        <v>456.8247136642036</v>
       </c>
       <c r="E65">
-        <v>299.95</v>
+        <v>305.8000000000001</v>
       </c>
       <c r="F65">
-        <v>368.55</v>
+        <v>374.4</v>
       </c>
       <c r="G65">
         <v>36</v>
@@ -6617,45 +6617,45 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M65">
-        <v>27.93609</v>
+        <v>33.69600000000001</v>
       </c>
       <c r="N65">
-        <v>28.66390999999999</v>
+        <v>22.90399999999999</v>
       </c>
       <c r="O65">
-        <v>7.165977499999998</v>
+        <v>5.725999999999997</v>
       </c>
       <c r="P65">
-        <v>21.49793249999999</v>
+        <v>17.17799999999999</v>
       </c>
       <c r="Q65">
-        <v>43.49793249999999</v>
+        <v>39.17799999999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1289452691055699</v>
+        <v>0.1310012846620875</v>
       </c>
       <c r="T65">
-        <v>1.286230869698886</v>
+        <v>1.31803677646691</v>
       </c>
       <c r="U65">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V65">
         <v>0.25</v>
       </c>
       <c r="W65">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.026053037486634</v>
+        <v>1.679724596391263</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.0903604624783515</v>
+        <v>0.09048617538764211</v>
       </c>
       <c r="C66">
-        <v>118.4247136642035</v>
+        <v>111.4482853953998</v>
       </c>
       <c r="D66">
-        <v>456.8247136642036</v>
+        <v>455.6982853953998</v>
       </c>
       <c r="E66">
-        <v>305.8000000000001</v>
+        <v>311.65</v>
       </c>
       <c r="F66">
-        <v>374.4</v>
+        <v>380.25</v>
       </c>
       <c r="G66">
         <v>36</v>
@@ -6699,28 +6699,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M66">
-        <v>33.69600000000001</v>
+        <v>34.2225</v>
       </c>
       <c r="N66">
-        <v>22.90399999999999</v>
+        <v>22.3775</v>
       </c>
       <c r="O66">
-        <v>5.725999999999997</v>
+        <v>5.594374999999999</v>
       </c>
       <c r="P66">
-        <v>17.17799999999999</v>
+        <v>16.783125</v>
       </c>
       <c r="Q66">
-        <v>39.17799999999999</v>
+        <v>38.783125</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1310012846620875</v>
+        <v>0.1331747868218346</v>
       </c>
       <c r="T66">
-        <v>1.31803677646691</v>
+        <v>1.351660163621678</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.679724596391263</v>
+        <v>1.653882679523705</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09048617538764211</v>
+        <v>0.09061188829693273</v>
       </c>
       <c r="C67">
-        <v>111.4482853953998</v>
+        <v>104.4773985065755</v>
       </c>
       <c r="D67">
-        <v>455.6982853953998</v>
+        <v>454.5773985065755</v>
       </c>
       <c r="E67">
-        <v>311.65</v>
+        <v>317.5</v>
       </c>
       <c r="F67">
-        <v>380.25</v>
+        <v>386.1</v>
       </c>
       <c r="G67">
         <v>36</v>
@@ -6781,28 +6781,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M67">
-        <v>34.2225</v>
+        <v>34.749</v>
       </c>
       <c r="N67">
-        <v>22.3775</v>
+        <v>21.85099999999999</v>
       </c>
       <c r="O67">
-        <v>5.594374999999999</v>
+        <v>5.462749999999998</v>
       </c>
       <c r="P67">
-        <v>16.783125</v>
+        <v>16.38824999999999</v>
       </c>
       <c r="Q67">
-        <v>38.783125</v>
+        <v>38.38824999999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1331747868218346</v>
+        <v>0.1354761420498022</v>
       </c>
       <c r="T67">
-        <v>1.351660163621678</v>
+        <v>1.387261397079668</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.653882679523705</v>
+        <v>1.628823851046073</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09061188829693273</v>
+        <v>0.09073760120622336</v>
       </c>
       <c r="C68">
-        <v>104.4773985065755</v>
+        <v>97.51201220745384</v>
       </c>
       <c r="D68">
-        <v>454.5773985065755</v>
+        <v>453.4620122074539</v>
       </c>
       <c r="E68">
-        <v>317.5</v>
+        <v>323.35</v>
       </c>
       <c r="F68">
-        <v>386.1</v>
+        <v>391.95</v>
       </c>
       <c r="G68">
         <v>36</v>
@@ -6863,28 +6863,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M68">
-        <v>34.749</v>
+        <v>35.2755</v>
       </c>
       <c r="N68">
-        <v>21.85099999999999</v>
+        <v>21.32449999999999</v>
       </c>
       <c r="O68">
-        <v>5.462749999999998</v>
+        <v>5.331124999999998</v>
       </c>
       <c r="P68">
-        <v>16.38824999999999</v>
+        <v>15.993375</v>
       </c>
       <c r="Q68">
-        <v>38.38824999999999</v>
+        <v>37.99337499999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1354761420498022</v>
+        <v>0.137916973352192</v>
       </c>
       <c r="T68">
-        <v>1.387261397079668</v>
+        <v>1.425020281050263</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.628823851046073</v>
+        <v>1.604513047299117</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09073760120622336</v>
+        <v>0.09086331411551397</v>
       </c>
       <c r="C69">
-        <v>97.51201220745384</v>
+        <v>90.5520861071231</v>
       </c>
       <c r="D69">
-        <v>453.4620122074539</v>
+        <v>452.3520861071231</v>
       </c>
       <c r="E69">
-        <v>323.35</v>
+        <v>329.2</v>
       </c>
       <c r="F69">
-        <v>391.95</v>
+        <v>397.8</v>
       </c>
       <c r="G69">
         <v>36</v>
@@ -6945,28 +6945,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M69">
-        <v>35.2755</v>
+        <v>35.802</v>
       </c>
       <c r="N69">
-        <v>21.32449999999999</v>
+        <v>20.79799999999999</v>
       </c>
       <c r="O69">
-        <v>5.331124999999998</v>
+        <v>5.199499999999999</v>
       </c>
       <c r="P69">
-        <v>15.993375</v>
+        <v>15.5985</v>
       </c>
       <c r="Q69">
-        <v>37.99337499999999</v>
+        <v>37.59849999999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.137916973352192</v>
+        <v>0.1405103566109812</v>
       </c>
       <c r="T69">
-        <v>1.425020281050263</v>
+        <v>1.465139095269021</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.604513047299117</v>
+        <v>1.580917267191777</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09086331411551397</v>
+        <v>0.0909890270248046</v>
       </c>
       <c r="C70">
-        <v>90.5520861071231</v>
+        <v>83.59758020916007</v>
       </c>
       <c r="D70">
-        <v>452.3520861071231</v>
+        <v>451.2475802091601</v>
       </c>
       <c r="E70">
-        <v>329.2</v>
+        <v>335.0500000000001</v>
       </c>
       <c r="F70">
-        <v>397.8</v>
+        <v>403.65</v>
       </c>
       <c r="G70">
         <v>36</v>
@@ -7027,28 +7027,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M70">
-        <v>35.802</v>
+        <v>36.3285</v>
       </c>
       <c r="N70">
-        <v>20.79799999999999</v>
+        <v>20.2715</v>
       </c>
       <c r="O70">
-        <v>5.199499999999999</v>
+        <v>5.067874999999999</v>
       </c>
       <c r="P70">
-        <v>15.5985</v>
+        <v>15.203625</v>
       </c>
       <c r="Q70">
-        <v>37.59849999999999</v>
+        <v>37.203625</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1405103566109812</v>
+        <v>0.1432710549187245</v>
       </c>
       <c r="T70">
-        <v>1.465139095269021</v>
+        <v>1.507846220082537</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.580917267191777</v>
+        <v>1.558005422739722</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0909890270248046</v>
+        <v>0.09111473993409522</v>
       </c>
       <c r="C71">
-        <v>83.59758020916007</v>
+        <v>76.648454906827</v>
       </c>
       <c r="D71">
-        <v>451.2475802091601</v>
+        <v>450.1484549068271</v>
       </c>
       <c r="E71">
-        <v>335.0500000000001</v>
+        <v>340.9000000000001</v>
       </c>
       <c r="F71">
-        <v>403.65</v>
+        <v>409.5000000000001</v>
       </c>
       <c r="G71">
         <v>36</v>
@@ -7109,28 +7109,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M71">
-        <v>36.3285</v>
+        <v>36.855</v>
       </c>
       <c r="N71">
-        <v>20.2715</v>
+        <v>19.74499999999999</v>
       </c>
       <c r="O71">
-        <v>5.067874999999999</v>
+        <v>4.936249999999998</v>
       </c>
       <c r="P71">
-        <v>15.203625</v>
+        <v>14.80874999999999</v>
       </c>
       <c r="Q71">
-        <v>37.203625</v>
+        <v>36.80874999999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1432710549187245</v>
+        <v>0.1462157997803174</v>
       </c>
       <c r="T71">
-        <v>1.507846220082537</v>
+        <v>1.553400486550287</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.558005422739722</v>
+        <v>1.535748202414869</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09111473993409522</v>
+        <v>0.09124045284338583</v>
       </c>
       <c r="C72">
-        <v>76.648454906827</v>
+        <v>69.70467097833625</v>
       </c>
       <c r="D72">
-        <v>450.1484549068271</v>
+        <v>449.0546709783363</v>
       </c>
       <c r="E72">
-        <v>340.9000000000001</v>
+        <v>346.75</v>
       </c>
       <c r="F72">
-        <v>409.5000000000001</v>
+        <v>415.35</v>
       </c>
       <c r="G72">
         <v>36</v>
@@ -7191,28 +7191,28 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M72">
-        <v>36.855</v>
+        <v>37.3815</v>
       </c>
       <c r="N72">
-        <v>19.74499999999999</v>
+        <v>19.21849999999999</v>
       </c>
       <c r="O72">
-        <v>4.936249999999998</v>
+        <v>4.804624999999998</v>
       </c>
       <c r="P72">
-        <v>14.80874999999999</v>
+        <v>14.41387499999999</v>
       </c>
       <c r="Q72">
-        <v>36.80874999999999</v>
+        <v>36.41387499999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1462157997803174</v>
+        <v>0.1493636304944339</v>
       </c>
       <c r="T72">
-        <v>1.553400486550287</v>
+        <v>1.602096426567538</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.535748202414869</v>
+        <v>1.514117946042828</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09124045284338583</v>
+        <v>0.1248303027196831</v>
       </c>
       <c r="C73">
-        <v>69.70467097833631</v>
+        <v>-112.9199170912565</v>
       </c>
       <c r="D73">
-        <v>449.0546709783363</v>
+        <v>272.2800829087435</v>
       </c>
       <c r="E73">
-        <v>346.75</v>
+        <v>352.6</v>
       </c>
       <c r="F73">
-        <v>415.35</v>
+        <v>421.2</v>
       </c>
       <c r="G73">
         <v>36</v>
@@ -7273,45 +7273,45 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M73">
-        <v>37.3815</v>
+        <v>61.83216</v>
       </c>
       <c r="N73">
-        <v>19.2185</v>
+        <v>-5.232160000000007</v>
       </c>
       <c r="O73">
-        <v>4.804625</v>
+        <v>-1.308040000000002</v>
       </c>
       <c r="P73">
-        <v>14.413875</v>
+        <v>-3.924120000000006</v>
       </c>
       <c r="Q73">
-        <v>36.413875</v>
+        <v>18.07587999999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1493636304944339</v>
+        <v>0.1547226318132761</v>
       </c>
       <c r="T73">
-        <v>1.602096426567537</v>
+        <v>1.684998472603372</v>
       </c>
       <c r="U73">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.25</v>
+        <v>0.2288453128598451</v>
       </c>
       <c r="W73">
-        <v>0.0675</v>
+        <v>0.1132055080721747</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y73">
-        <v>1.514117946042829</v>
+        <v>0.9153812514393803</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1248303027196831</v>
+        <v>0.1258403027196831</v>
       </c>
       <c r="C74">
-        <v>-112.9199170912565</v>
+        <v>-121.9551363641692</v>
       </c>
       <c r="D74">
-        <v>272.2800829087435</v>
+        <v>269.0948636358308</v>
       </c>
       <c r="E74">
-        <v>352.6</v>
+        <v>358.45</v>
       </c>
       <c r="F74">
-        <v>421.2</v>
+        <v>427.05</v>
       </c>
       <c r="G74">
         <v>36</v>
@@ -7355,37 +7355,37 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M74">
-        <v>61.83216</v>
+        <v>62.69094</v>
       </c>
       <c r="N74">
-        <v>-5.232160000000007</v>
+        <v>-6.09094000000001</v>
       </c>
       <c r="O74">
-        <v>-1.308040000000002</v>
+        <v>-1.522735000000003</v>
       </c>
       <c r="P74">
-        <v>-3.924120000000006</v>
+        <v>-4.568205000000008</v>
       </c>
       <c r="Q74">
-        <v>18.07587999999999</v>
+        <v>17.43179499999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1547226318132761</v>
+        <v>0.158756803361916</v>
       </c>
       <c r="T74">
-        <v>1.684998472603372</v>
+        <v>1.747405823440535</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.2288453128598451</v>
+        <v>0.2257104455603951</v>
       </c>
       <c r="W74">
-        <v>0.1132055080721747</v>
+        <v>0.113665706591734</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.9153812514393803</v>
+        <v>0.9028417822415805</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1258403027196831</v>
+        <v>0.1268503027196831</v>
       </c>
       <c r="C75">
-        <v>-121.9551363641692</v>
+        <v>-130.9166939327857</v>
       </c>
       <c r="D75">
-        <v>269.0948636358308</v>
+        <v>265.9833060672142</v>
       </c>
       <c r="E75">
-        <v>358.45</v>
+        <v>364.3</v>
       </c>
       <c r="F75">
-        <v>427.05</v>
+        <v>432.9</v>
       </c>
       <c r="G75">
         <v>36</v>
@@ -7437,37 +7437,37 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M75">
-        <v>62.69094</v>
+        <v>63.54972</v>
       </c>
       <c r="N75">
-        <v>-6.09094000000001</v>
+        <v>-6.949720000000006</v>
       </c>
       <c r="O75">
-        <v>-1.522735000000003</v>
+        <v>-1.737430000000002</v>
       </c>
       <c r="P75">
-        <v>-4.568205000000008</v>
+        <v>-5.212290000000005</v>
       </c>
       <c r="Q75">
-        <v>17.43179499999999</v>
+        <v>16.78771</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.158756803361916</v>
+        <v>0.1631012957989127</v>
       </c>
       <c r="T75">
-        <v>1.747405823440535</v>
+        <v>1.814613739726709</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.2257104455603951</v>
+        <v>0.2226603044041736</v>
       </c>
       <c r="W75">
-        <v>0.113665706591734</v>
+        <v>0.1141134673134673</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.9028417822415805</v>
+        <v>0.8906412176166943</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1268503027196831</v>
+        <v>0.1278603027196832</v>
       </c>
       <c r="C76">
-        <v>-130.9166939327857</v>
+        <v>-139.8071158503039</v>
       </c>
       <c r="D76">
-        <v>265.9833060672142</v>
+        <v>262.9428841496961</v>
       </c>
       <c r="E76">
-        <v>364.3</v>
+        <v>370.15</v>
       </c>
       <c r="F76">
-        <v>432.9</v>
+        <v>438.75</v>
       </c>
       <c r="G76">
         <v>36</v>
@@ -7519,37 +7519,37 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M76">
-        <v>63.54972</v>
+        <v>64.4085</v>
       </c>
       <c r="N76">
-        <v>-6.949720000000006</v>
+        <v>-7.808500000000009</v>
       </c>
       <c r="O76">
-        <v>-1.737430000000002</v>
+        <v>-1.952125000000002</v>
       </c>
       <c r="P76">
-        <v>-5.212290000000005</v>
+        <v>-5.856375000000007</v>
       </c>
       <c r="Q76">
-        <v>16.78771</v>
+        <v>16.14362499999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1631012957989127</v>
+        <v>0.1677933476308693</v>
       </c>
       <c r="T76">
-        <v>1.814613739726709</v>
+        <v>1.887198289315777</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.2226603044041736</v>
+        <v>0.2196915003454513</v>
       </c>
       <c r="W76">
-        <v>0.1141134673134673</v>
+        <v>0.1145492877492878</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8906412176166943</v>
+        <v>0.8787660013818051</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1278603027196832</v>
+        <v>0.1288703027196831</v>
       </c>
       <c r="C77">
-        <v>-139.8071158503039</v>
+        <v>-148.6288139752718</v>
       </c>
       <c r="D77">
-        <v>262.9428841496961</v>
+        <v>259.9711860247282</v>
       </c>
       <c r="E77">
-        <v>370.15</v>
+        <v>376</v>
       </c>
       <c r="F77">
-        <v>438.75</v>
+        <v>444.6</v>
       </c>
       <c r="G77">
         <v>36</v>
@@ -7601,37 +7601,37 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M77">
-        <v>64.4085</v>
+        <v>65.26728000000001</v>
       </c>
       <c r="N77">
-        <v>-7.808500000000009</v>
+        <v>-8.667280000000019</v>
       </c>
       <c r="O77">
-        <v>-1.952125000000002</v>
+        <v>-2.166820000000005</v>
       </c>
       <c r="P77">
-        <v>-5.856375000000007</v>
+        <v>-6.500460000000015</v>
       </c>
       <c r="Q77">
-        <v>16.14362499999999</v>
+        <v>15.49953999999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1677933476308693</v>
+        <v>0.1728764037821555</v>
       </c>
       <c r="T77">
-        <v>1.887198289315777</v>
+        <v>1.965831551370602</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.2196915003454513</v>
+        <v>0.2168008227093269</v>
       </c>
       <c r="W77">
-        <v>0.1145492877492878</v>
+        <v>0.1149736392262708</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8787660013818051</v>
+        <v>0.8672032908373075</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1288703027196831</v>
+        <v>0.1298803027196831</v>
       </c>
       <c r="C78">
-        <v>-148.6288139752718</v>
+        <v>-157.3840923524366</v>
       </c>
       <c r="D78">
-        <v>259.9711860247282</v>
+        <v>257.0659076475634</v>
       </c>
       <c r="E78">
-        <v>376</v>
+        <v>381.85</v>
       </c>
       <c r="F78">
-        <v>444.6</v>
+        <v>450.45</v>
       </c>
       <c r="G78">
         <v>36</v>
@@ -7683,37 +7683,37 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M78">
-        <v>65.26728000000001</v>
+        <v>66.12606000000001</v>
       </c>
       <c r="N78">
-        <v>-8.667280000000019</v>
+        <v>-9.526060000000015</v>
       </c>
       <c r="O78">
-        <v>-2.166820000000005</v>
+        <v>-2.381515000000004</v>
       </c>
       <c r="P78">
-        <v>-6.500460000000015</v>
+        <v>-7.144545000000011</v>
       </c>
       <c r="Q78">
-        <v>15.49953999999999</v>
+        <v>14.85545499999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1728764037821555</v>
+        <v>0.1784014648161622</v>
       </c>
       <c r="T78">
-        <v>1.965831551370602</v>
+        <v>2.051302488386714</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.2168008227093269</v>
+        <v>0.2139852276092058</v>
       </c>
       <c r="W78">
-        <v>0.1149736392262708</v>
+        <v>0.1153869685869686</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8672032908373075</v>
+        <v>0.855940910436823</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1298803027196831</v>
+        <v>0.1308903027196831</v>
       </c>
       <c r="C79">
-        <v>-157.3840923524366</v>
+        <v>-166.0751531704674</v>
       </c>
       <c r="D79">
-        <v>257.0659076475634</v>
+        <v>254.2248468295326</v>
       </c>
       <c r="E79">
-        <v>381.85</v>
+        <v>387.7</v>
       </c>
       <c r="F79">
-        <v>450.45</v>
+        <v>456.3</v>
       </c>
       <c r="G79">
         <v>36</v>
@@ -7765,37 +7765,37 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M79">
-        <v>66.12606000000001</v>
+        <v>66.98484000000001</v>
       </c>
       <c r="N79">
-        <v>-9.526060000000015</v>
+        <v>-10.38484000000001</v>
       </c>
       <c r="O79">
-        <v>-2.381515000000004</v>
+        <v>-2.596210000000003</v>
       </c>
       <c r="P79">
-        <v>-7.144545000000011</v>
+        <v>-7.788630000000008</v>
       </c>
       <c r="Q79">
-        <v>14.85545499999999</v>
+        <v>14.21136999999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1784014648161622</v>
+        <v>0.1844288041259878</v>
       </c>
       <c r="T79">
-        <v>2.051302488386714</v>
+        <v>2.144543510586111</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.2139852276092058</v>
+        <v>0.2112418272552416</v>
       </c>
       <c r="W79">
-        <v>0.1153869685869686</v>
+        <v>0.1157896997589305</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.855940910436823</v>
+        <v>0.8449673090209664</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1308903027196831</v>
+        <v>0.1319003027196831</v>
       </c>
       <c r="C80">
-        <v>-166.0751531704674</v>
+        <v>-174.7041023289349</v>
       </c>
       <c r="D80">
-        <v>254.2248468295326</v>
+        <v>251.4458976710651</v>
       </c>
       <c r="E80">
-        <v>387.7</v>
+        <v>393.5500000000001</v>
       </c>
       <c r="F80">
-        <v>456.3</v>
+        <v>462.15</v>
       </c>
       <c r="G80">
         <v>36</v>
@@ -7847,37 +7847,37 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M80">
-        <v>66.98484000000001</v>
+        <v>67.84362000000002</v>
       </c>
       <c r="N80">
-        <v>-10.38484000000001</v>
+        <v>-11.24362000000002</v>
       </c>
       <c r="O80">
-        <v>-2.596210000000003</v>
+        <v>-2.810905000000005</v>
       </c>
       <c r="P80">
-        <v>-7.788630000000008</v>
+        <v>-8.432715000000016</v>
       </c>
       <c r="Q80">
-        <v>14.21136999999999</v>
+        <v>13.56728499999998</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1844288041259878</v>
+        <v>0.1910301757510348</v>
       </c>
       <c r="T80">
-        <v>2.144543510586111</v>
+        <v>2.24666463013783</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.2112418272552416</v>
+        <v>0.2085678800747955</v>
       </c>
       <c r="W80">
-        <v>0.1157896997589305</v>
+        <v>0.11618223520502</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8449673090209664</v>
+        <v>0.8342715202991818</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1319003027196831</v>
+        <v>0.1329103027196831</v>
       </c>
       <c r="C81">
-        <v>-174.7041023289349</v>
+        <v>-183.272954644119</v>
       </c>
       <c r="D81">
-        <v>251.4458976710651</v>
+        <v>248.727045355881</v>
       </c>
       <c r="E81">
-        <v>393.5500000000001</v>
+        <v>399.4</v>
       </c>
       <c r="F81">
-        <v>462.15</v>
+        <v>468</v>
       </c>
       <c r="G81">
         <v>36</v>
@@ -7929,37 +7929,37 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M81">
-        <v>67.84362000000002</v>
+        <v>68.70240000000001</v>
       </c>
       <c r="N81">
-        <v>-11.24362000000002</v>
+        <v>-12.10240000000002</v>
       </c>
       <c r="O81">
-        <v>-2.810905000000005</v>
+        <v>-3.025600000000004</v>
       </c>
       <c r="P81">
-        <v>-8.432715000000016</v>
+        <v>-9.076800000000013</v>
       </c>
       <c r="Q81">
-        <v>13.56728499999998</v>
+        <v>12.92319999999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1910301757510348</v>
+        <v>0.1982916845385866</v>
       </c>
       <c r="T81">
-        <v>2.24666463013783</v>
+        <v>2.358997861644722</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.2085678800747955</v>
+        <v>0.2059607815738605</v>
       </c>
       <c r="W81">
-        <v>0.11618223520502</v>
+        <v>0.1165649572649573</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8342715202991818</v>
+        <v>0.8238431262954422</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1329103027196831</v>
+        <v>0.1339203027196831</v>
       </c>
       <c r="C82">
-        <v>-183.272954644119</v>
+        <v>-191.7836387206928</v>
       </c>
       <c r="D82">
-        <v>248.727045355881</v>
+        <v>246.0663612793072</v>
       </c>
       <c r="E82">
-        <v>399.4</v>
+        <v>405.25</v>
       </c>
       <c r="F82">
-        <v>468</v>
+        <v>473.85</v>
       </c>
       <c r="G82">
         <v>36</v>
@@ -8011,37 +8011,37 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M82">
-        <v>68.70240000000001</v>
+        <v>69.56118000000001</v>
       </c>
       <c r="N82">
-        <v>-12.10240000000002</v>
+        <v>-12.96118000000001</v>
       </c>
       <c r="O82">
-        <v>-3.025600000000004</v>
+        <v>-3.240295000000003</v>
       </c>
       <c r="P82">
-        <v>-9.076800000000013</v>
+        <v>-9.72088500000001</v>
       </c>
       <c r="Q82">
-        <v>12.92319999999999</v>
+        <v>12.27911499999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1982916845385866</v>
+        <v>0.2063175626721964</v>
       </c>
       <c r="T82">
-        <v>2.358997861644722</v>
+        <v>2.483155643836549</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.2059607815738605</v>
+        <v>0.2034180558754178</v>
       </c>
       <c r="W82">
-        <v>0.1165649572649573</v>
+        <v>0.1169382293974887</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8238431262954422</v>
+        <v>0.8136722235016713</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1339203027196831</v>
+        <v>0.1349303027196831</v>
       </c>
       <c r="C83">
-        <v>-191.7836387206928</v>
+        <v>-200.2380015140336</v>
       </c>
       <c r="D83">
-        <v>246.0663612793072</v>
+        <v>243.4619984859665</v>
       </c>
       <c r="E83">
-        <v>405.25</v>
+        <v>411.1</v>
       </c>
       <c r="F83">
-        <v>473.85</v>
+        <v>479.7</v>
       </c>
       <c r="G83">
         <v>36</v>
@@ -8093,37 +8093,37 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M83">
-        <v>69.56118000000001</v>
+        <v>70.41996000000002</v>
       </c>
       <c r="N83">
-        <v>-12.96118000000001</v>
+        <v>-13.81996000000002</v>
       </c>
       <c r="O83">
-        <v>-3.240295000000003</v>
+        <v>-3.454990000000006</v>
       </c>
       <c r="P83">
-        <v>-9.72088500000001</v>
+        <v>-10.36497000000002</v>
       </c>
       <c r="Q83">
-        <v>12.27911499999999</v>
+        <v>11.63502999999998</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2063175626721964</v>
+        <v>0.215235205042874</v>
       </c>
       <c r="T83">
-        <v>2.483155643836549</v>
+        <v>2.621108735160802</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.2034180558754178</v>
+        <v>0.2009373478769371</v>
       </c>
       <c r="W83">
-        <v>0.1169382293974887</v>
+        <v>0.1173023973316657</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8136722235016713</v>
+        <v>0.8037493915077484</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1349303027196831</v>
+        <v>0.1823782856196127</v>
       </c>
       <c r="C84">
-        <v>-200.2380015140336</v>
+        <v>-286.9402619251636</v>
       </c>
       <c r="D84">
-        <v>243.4619984859665</v>
+        <v>162.6097380748365</v>
       </c>
       <c r="E84">
-        <v>411.1</v>
+        <v>416.95</v>
       </c>
       <c r="F84">
-        <v>479.7</v>
+        <v>485.5500000000001</v>
       </c>
       <c r="G84">
         <v>36</v>
@@ -8175,45 +8175,45 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M84">
-        <v>70.41996000000002</v>
+        <v>97.49844000000002</v>
       </c>
       <c r="N84">
-        <v>-13.81996000000002</v>
+        <v>-40.89844000000002</v>
       </c>
       <c r="O84">
-        <v>-3.454990000000006</v>
+        <v>-10.22461000000001</v>
       </c>
       <c r="P84">
-        <v>-10.36497000000002</v>
+        <v>-30.67383000000002</v>
       </c>
       <c r="Q84">
-        <v>11.63502999999998</v>
+        <v>-8.673830000000017</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.215235205042874</v>
+        <v>0.234719528280276</v>
       </c>
       <c r="T84">
-        <v>2.621108735160802</v>
+        <v>2.922525018886065</v>
       </c>
       <c r="U84">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.2009373478769371</v>
+        <v>0.1451305272166405</v>
       </c>
       <c r="W84">
-        <v>0.1173023973316657</v>
+        <v>0.1716577901348986</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.8037493915077484</v>
+        <v>0.5805221088665622</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1823782856196127</v>
+        <v>0.1839282856196127</v>
       </c>
       <c r="C85">
-        <v>-286.9402619251636</v>
+        <v>-294.5354223273313</v>
       </c>
       <c r="D85">
-        <v>162.6097380748365</v>
+        <v>160.8645776726687</v>
       </c>
       <c r="E85">
-        <v>416.95</v>
+        <v>422.8000000000001</v>
       </c>
       <c r="F85">
-        <v>485.5500000000001</v>
+        <v>491.4</v>
       </c>
       <c r="G85">
         <v>36</v>
@@ -8257,37 +8257,37 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M85">
-        <v>97.49844000000002</v>
+        <v>98.67312000000001</v>
       </c>
       <c r="N85">
-        <v>-40.89844000000002</v>
+        <v>-42.07312000000002</v>
       </c>
       <c r="O85">
-        <v>-10.22461000000001</v>
+        <v>-10.51828</v>
       </c>
       <c r="P85">
-        <v>-30.67383000000002</v>
+        <v>-31.55484000000001</v>
       </c>
       <c r="Q85">
-        <v>-8.673830000000017</v>
+        <v>-9.554840000000013</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.234719528280276</v>
+        <v>0.2465269987977932</v>
       </c>
       <c r="T85">
-        <v>2.922525018886065</v>
+        <v>3.105182832566444</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1451305272166405</v>
+        <v>0.1434027828450139</v>
       </c>
       <c r="W85">
-        <v>0.1716577901348986</v>
+        <v>0.1720047212047212</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5805221088665622</v>
+        <v>0.5736111313800556</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1839282856196127</v>
+        <v>0.1854782856196127</v>
       </c>
       <c r="C86">
-        <v>-294.5354223273313</v>
+        <v>-302.093521651825</v>
       </c>
       <c r="D86">
-        <v>160.8645776726687</v>
+        <v>159.1564783481751</v>
       </c>
       <c r="E86">
-        <v>422.8</v>
+        <v>428.65</v>
       </c>
       <c r="F86">
-        <v>491.4</v>
+        <v>497.25</v>
       </c>
       <c r="G86">
         <v>36</v>
@@ -8339,37 +8339,37 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M86">
-        <v>98.67312</v>
+        <v>99.84780000000001</v>
       </c>
       <c r="N86">
-        <v>-42.07312</v>
+        <v>-43.24780000000001</v>
       </c>
       <c r="O86">
-        <v>-10.51828</v>
+        <v>-10.81195</v>
       </c>
       <c r="P86">
-        <v>-31.55484</v>
+        <v>-32.43585000000001</v>
       </c>
       <c r="Q86">
-        <v>-9.554840000000002</v>
+        <v>-10.43585000000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2465269987977931</v>
+        <v>0.259908798717646</v>
       </c>
       <c r="T86">
-        <v>3.105182832566442</v>
+        <v>3.312195021404205</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1434027828450139</v>
+        <v>0.1417156912821314</v>
       </c>
       <c r="W86">
-        <v>0.1720047212047212</v>
+        <v>0.172343489190548</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5736111313800556</v>
+        <v>0.5668627651285255</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1854782856196127</v>
+        <v>0.1870282856196127</v>
       </c>
       <c r="C87">
-        <v>-302.093521651825</v>
+        <v>-309.6157280654527</v>
       </c>
       <c r="D87">
-        <v>159.1564783481751</v>
+        <v>157.4842719345473</v>
       </c>
       <c r="E87">
-        <v>428.65</v>
+        <v>434.5</v>
       </c>
       <c r="F87">
-        <v>497.25</v>
+        <v>503.1</v>
       </c>
       <c r="G87">
         <v>36</v>
@@ -8421,37 +8421,37 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M87">
-        <v>99.84780000000001</v>
+        <v>101.02248</v>
       </c>
       <c r="N87">
-        <v>-43.24780000000001</v>
+        <v>-44.42248000000001</v>
       </c>
       <c r="O87">
-        <v>-10.81195</v>
+        <v>-11.10562</v>
       </c>
       <c r="P87">
-        <v>-32.43585000000001</v>
+        <v>-33.31686000000001</v>
       </c>
       <c r="Q87">
-        <v>-10.43585000000001</v>
+        <v>-11.31686000000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.259908798717646</v>
+        <v>0.2752022843403349</v>
       </c>
       <c r="T87">
-        <v>3.312195021404205</v>
+        <v>3.548780380075934</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1417156912821314</v>
+        <v>0.1400678344067578</v>
       </c>
       <c r="W87">
-        <v>0.172343489190548</v>
+        <v>0.1726743788511231</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5668627651285255</v>
+        <v>0.5602713376270311</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1870282856196127</v>
+        <v>0.1885782856196127</v>
       </c>
       <c r="C88">
-        <v>-309.6157280654527</v>
+        <v>-317.1031611512514</v>
       </c>
       <c r="D88">
-        <v>157.4842719345473</v>
+        <v>155.8468388487487</v>
       </c>
       <c r="E88">
-        <v>434.5</v>
+        <v>440.35</v>
       </c>
       <c r="F88">
-        <v>503.1</v>
+        <v>508.95</v>
       </c>
       <c r="G88">
         <v>36</v>
@@ -8503,37 +8503,37 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M88">
-        <v>101.02248</v>
+        <v>102.19716</v>
       </c>
       <c r="N88">
-        <v>-44.42248000000001</v>
+        <v>-45.59716</v>
       </c>
       <c r="O88">
-        <v>-11.10562</v>
+        <v>-11.39929</v>
       </c>
       <c r="P88">
-        <v>-33.31686000000001</v>
+        <v>-34.19787</v>
       </c>
       <c r="Q88">
-        <v>-11.31686000000001</v>
+        <v>-12.19787</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2752022843403349</v>
+        <v>0.2928486139049761</v>
       </c>
       <c r="T88">
-        <v>3.548780380075934</v>
+        <v>3.821763486235621</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1400678344067578</v>
+        <v>0.1384578592986341</v>
       </c>
       <c r="W88">
-        <v>0.1726743788511231</v>
+        <v>0.1729976618528343</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5602713376270311</v>
+        <v>0.5538314371945365</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1885782856196127</v>
+        <v>0.1901282856196127</v>
       </c>
       <c r="C89">
-        <v>-317.1031611512514</v>
+        <v>-324.5568944082288</v>
       </c>
       <c r="D89">
-        <v>155.8468388487487</v>
+        <v>154.2431055917712</v>
       </c>
       <c r="E89">
-        <v>440.35</v>
+        <v>446.1999999999999</v>
       </c>
       <c r="F89">
-        <v>508.95</v>
+        <v>514.8</v>
       </c>
       <c r="G89">
         <v>36</v>
@@ -8585,37 +8585,37 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M89">
-        <v>102.19716</v>
+        <v>103.37184</v>
       </c>
       <c r="N89">
-        <v>-45.59716</v>
+        <v>-46.77184</v>
       </c>
       <c r="O89">
-        <v>-11.39929</v>
+        <v>-11.69296</v>
       </c>
       <c r="P89">
-        <v>-34.19787</v>
+        <v>-35.07888</v>
       </c>
       <c r="Q89">
-        <v>-12.19787</v>
+        <v>-13.07888</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2928486139049761</v>
+        <v>0.3134359983970575</v>
       </c>
       <c r="T89">
-        <v>3.821763486235621</v>
+        <v>4.140243776755256</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1384578592986341</v>
+        <v>0.1368844745338769</v>
       </c>
       <c r="W89">
-        <v>0.1729976618528343</v>
+        <v>0.1733135975135975</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5538314371945365</v>
+        <v>0.5475378981355077</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1901282856196127</v>
+        <v>0.1916782856196127</v>
       </c>
       <c r="C90">
-        <v>-324.5568944082288</v>
+        <v>-331.9779575983382</v>
       </c>
       <c r="D90">
-        <v>154.2431055917712</v>
+        <v>152.6720424016618</v>
       </c>
       <c r="E90">
-        <v>446.1999999999999</v>
+        <v>452.05</v>
       </c>
       <c r="F90">
-        <v>514.8</v>
+        <v>520.65</v>
       </c>
       <c r="G90">
         <v>36</v>
@@ -8667,37 +8667,37 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M90">
-        <v>103.37184</v>
+        <v>104.54652</v>
       </c>
       <c r="N90">
-        <v>-46.77184</v>
+        <v>-47.94652000000001</v>
       </c>
       <c r="O90">
-        <v>-11.69296</v>
+        <v>-11.98663</v>
       </c>
       <c r="P90">
-        <v>-35.07888</v>
+        <v>-35.95989</v>
       </c>
       <c r="Q90">
-        <v>-13.07888</v>
+        <v>-13.95989</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3134359983970575</v>
+        <v>0.3377665437058809</v>
       </c>
       <c r="T90">
-        <v>4.140243776755256</v>
+        <v>4.516629574642098</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1368844745338769</v>
+        <v>0.1353464467301255</v>
       </c>
       <c r="W90">
-        <v>0.1733135975135975</v>
+        <v>0.1736224334965908</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5475378981355077</v>
+        <v>0.5413857869205019</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1916782856196127</v>
+        <v>0.1932282856196127</v>
       </c>
       <c r="C91">
-        <v>-331.9779575983382</v>
+        <v>-339.3673389514672</v>
       </c>
       <c r="D91">
-        <v>152.6720424016618</v>
+        <v>151.1326610485328</v>
       </c>
       <c r="E91">
-        <v>452.05</v>
+        <v>457.9</v>
       </c>
       <c r="F91">
-        <v>520.65</v>
+        <v>526.5</v>
       </c>
       <c r="G91">
         <v>36</v>
@@ -8749,37 +8749,37 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M91">
-        <v>104.54652</v>
+        <v>105.7212</v>
       </c>
       <c r="N91">
-        <v>-47.94652000000001</v>
+        <v>-49.12120000000002</v>
       </c>
       <c r="O91">
-        <v>-11.98663</v>
+        <v>-12.2803</v>
       </c>
       <c r="P91">
-        <v>-35.95989</v>
+        <v>-36.84090000000001</v>
       </c>
       <c r="Q91">
-        <v>-13.95989</v>
+        <v>-14.84090000000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3377665437058809</v>
+        <v>0.366963198076469</v>
       </c>
       <c r="T91">
-        <v>4.516629574642098</v>
+        <v>4.968292532106308</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1353464467301255</v>
+        <v>0.133842597322013</v>
       </c>
       <c r="W91">
-        <v>0.1736224334965908</v>
+        <v>0.1739244064577398</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5413857869205019</v>
+        <v>0.5353703892880519</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1932282856196127</v>
+        <v>0.1947782856196127</v>
       </c>
       <c r="C92">
-        <v>-339.3673389514672</v>
+        <v>-346.7259872383592</v>
       </c>
       <c r="D92">
-        <v>151.1326610485328</v>
+        <v>149.6240127616408</v>
       </c>
       <c r="E92">
-        <v>457.9</v>
+        <v>463.75</v>
       </c>
       <c r="F92">
-        <v>526.5</v>
+        <v>532.35</v>
       </c>
       <c r="G92">
         <v>36</v>
@@ -8831,37 +8831,37 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M92">
-        <v>105.7212</v>
+        <v>106.89588</v>
       </c>
       <c r="N92">
-        <v>-49.12120000000002</v>
+        <v>-50.29588000000001</v>
       </c>
       <c r="O92">
-        <v>-12.2803</v>
+        <v>-12.57397</v>
       </c>
       <c r="P92">
-        <v>-36.84090000000001</v>
+        <v>-37.72191000000001</v>
       </c>
       <c r="Q92">
-        <v>-14.84090000000001</v>
+        <v>-15.72191000000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.366963198076469</v>
+        <v>0.4026479978627435</v>
       </c>
       <c r="T92">
-        <v>4.968292532106308</v>
+        <v>5.520325035673677</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.133842597322013</v>
+        <v>0.1323717995492436</v>
       </c>
       <c r="W92">
-        <v>0.1739244064577398</v>
+        <v>0.1742197426505119</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5353703892880519</v>
+        <v>0.5294871981969744</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1947782856196127</v>
+        <v>0.1963282856196127</v>
       </c>
       <c r="C93">
-        <v>-346.7259872383592</v>
+        <v>-354.0548137206107</v>
       </c>
       <c r="D93">
-        <v>149.6240127616408</v>
+        <v>148.1451862793893</v>
       </c>
       <c r="E93">
-        <v>463.75</v>
+        <v>469.6</v>
       </c>
       <c r="F93">
-        <v>532.35</v>
+        <v>538.2</v>
       </c>
       <c r="G93">
         <v>36</v>
@@ -8913,37 +8913,37 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M93">
-        <v>106.89588</v>
+        <v>108.07056</v>
       </c>
       <c r="N93">
-        <v>-50.29588000000001</v>
+        <v>-51.47056000000002</v>
       </c>
       <c r="O93">
-        <v>-12.57397</v>
+        <v>-12.86764000000001</v>
       </c>
       <c r="P93">
-        <v>-37.72191000000001</v>
+        <v>-38.60292000000001</v>
       </c>
       <c r="Q93">
-        <v>-15.72191000000001</v>
+        <v>-16.60292000000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4026479978627435</v>
+        <v>0.4472539975955864</v>
       </c>
       <c r="T93">
-        <v>5.520325035673677</v>
+        <v>6.210365665132888</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1323717995492436</v>
+        <v>0.1309329756410996</v>
       </c>
       <c r="W93">
-        <v>0.1742197426505119</v>
+        <v>0.1745086584912672</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5294871981969744</v>
+        <v>0.5237319025643985</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1963282856196127</v>
+        <v>0.1978782856196127</v>
       </c>
       <c r="C94">
-        <v>-354.0548137206107</v>
+        <v>-361.3546939861591</v>
       </c>
       <c r="D94">
-        <v>148.1451862793893</v>
+        <v>146.6953060138409</v>
       </c>
       <c r="E94">
-        <v>469.6</v>
+        <v>475.45</v>
       </c>
       <c r="F94">
-        <v>538.2</v>
+        <v>544.0500000000001</v>
       </c>
       <c r="G94">
         <v>36</v>
@@ -8995,37 +8995,37 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M94">
-        <v>108.07056</v>
+        <v>109.24524</v>
       </c>
       <c r="N94">
-        <v>-51.47056000000002</v>
+        <v>-52.64524000000003</v>
       </c>
       <c r="O94">
-        <v>-12.86764000000001</v>
+        <v>-13.16131000000001</v>
       </c>
       <c r="P94">
-        <v>-38.60292000000001</v>
+        <v>-39.48393000000002</v>
       </c>
       <c r="Q94">
-        <v>-16.60292000000001</v>
+        <v>-17.48393000000002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4472539975955864</v>
+        <v>0.5046045686806703</v>
       </c>
       <c r="T94">
-        <v>6.210365665132888</v>
+        <v>7.097560760151873</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1309329756410996</v>
+        <v>0.1295250941825932</v>
       </c>
       <c r="W94">
-        <v>0.1745086584912672</v>
+        <v>0.1747913610881353</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5237319025643985</v>
+        <v>0.5181003767303727</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1978782856196127</v>
+        <v>0.1994282856196127</v>
       </c>
       <c r="C95">
-        <v>-361.3546939861591</v>
+        <v>-368.6264696780341</v>
       </c>
       <c r="D95">
-        <v>146.6953060138409</v>
+        <v>145.2735303219658</v>
       </c>
       <c r="E95">
-        <v>475.45</v>
+        <v>481.3</v>
       </c>
       <c r="F95">
-        <v>544.0500000000001</v>
+        <v>549.9</v>
       </c>
       <c r="G95">
         <v>36</v>
@@ -9077,37 +9077,37 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M95">
-        <v>109.24524</v>
+        <v>110.41992</v>
       </c>
       <c r="N95">
-        <v>-52.64524000000003</v>
+        <v>-53.81992000000001</v>
       </c>
       <c r="O95">
-        <v>-13.16131000000001</v>
+        <v>-13.45498</v>
       </c>
       <c r="P95">
-        <v>-39.48393000000002</v>
+        <v>-40.36494</v>
       </c>
       <c r="Q95">
-        <v>-17.48393000000002</v>
+        <v>-18.36494</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5046045686806703</v>
+        <v>0.5810719967941154</v>
       </c>
       <c r="T95">
-        <v>7.097560760151873</v>
+        <v>8.28048755351052</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1295250941825932</v>
+        <v>0.1281471676487358</v>
       </c>
       <c r="W95">
-        <v>0.1747913610881353</v>
+        <v>0.1750680487361339</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5181003767303727</v>
+        <v>0.5125886705949433</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1994282856196127</v>
+        <v>0.2009782856196127</v>
       </c>
       <c r="C96">
-        <v>-368.6264696780341</v>
+        <v>-375.8709501235444</v>
       </c>
       <c r="D96">
-        <v>145.2735303219658</v>
+        <v>143.8790498764556</v>
       </c>
       <c r="E96">
-        <v>481.3</v>
+        <v>487.15</v>
       </c>
       <c r="F96">
-        <v>549.9</v>
+        <v>555.75</v>
       </c>
       <c r="G96">
         <v>36</v>
@@ -9159,37 +9159,37 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M96">
-        <v>110.41992</v>
+        <v>111.5946</v>
       </c>
       <c r="N96">
-        <v>-53.81992000000001</v>
+        <v>-54.99460000000001</v>
       </c>
       <c r="O96">
-        <v>-13.45498</v>
+        <v>-13.74865</v>
       </c>
       <c r="P96">
-        <v>-40.36494</v>
+        <v>-41.24595000000001</v>
       </c>
       <c r="Q96">
-        <v>-18.36494</v>
+        <v>-19.24595000000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5810719967941154</v>
+        <v>0.6881263961529388</v>
       </c>
       <c r="T96">
-        <v>8.28048755351052</v>
+        <v>9.936585064212629</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1281471676487358</v>
+        <v>0.1267982500945386</v>
       </c>
       <c r="W96">
-        <v>0.1750680487361339</v>
+        <v>0.1753389113810166</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5125886705949433</v>
+        <v>0.5071930003781544</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2009782856196127</v>
+        <v>0.2025282856196127</v>
       </c>
       <c r="C97">
-        <v>-375.8709501235444</v>
+        <v>-383.0889138705226</v>
       </c>
       <c r="D97">
-        <v>143.8790498764556</v>
+        <v>142.5110861294775</v>
       </c>
       <c r="E97">
-        <v>487.15</v>
+        <v>493</v>
       </c>
       <c r="F97">
-        <v>555.75</v>
+        <v>561.6</v>
       </c>
       <c r="G97">
         <v>36</v>
@@ -9241,37 +9241,37 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M97">
-        <v>111.5946</v>
+        <v>112.76928</v>
       </c>
       <c r="N97">
-        <v>-54.99460000000001</v>
+        <v>-56.16928000000001</v>
       </c>
       <c r="O97">
-        <v>-13.74865</v>
+        <v>-14.04232</v>
       </c>
       <c r="P97">
-        <v>-41.24595000000001</v>
+        <v>-42.12696000000001</v>
       </c>
       <c r="Q97">
-        <v>-19.24595000000001</v>
+        <v>-20.12696000000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6881263961529388</v>
+        <v>0.8487079951911739</v>
       </c>
       <c r="T97">
-        <v>9.936585064212629</v>
+        <v>12.42073133026579</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1267982500945386</v>
+        <v>0.1254774349893872</v>
       </c>
       <c r="W97">
-        <v>0.1753389113810166</v>
+        <v>0.1756041310541311</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5071930003781544</v>
+        <v>0.5019097399575486</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2025282856196127</v>
+        <v>0.2386811612628005</v>
       </c>
       <c r="C98">
-        <v>-383.0889138705226</v>
+        <v>-414.8061497159907</v>
       </c>
       <c r="D98">
-        <v>142.5110861294774</v>
+        <v>116.6438502840092</v>
       </c>
       <c r="E98">
-        <v>493</v>
+        <v>498.8499999999999</v>
       </c>
       <c r="F98">
-        <v>561.6</v>
+        <v>567.4499999999999</v>
       </c>
       <c r="G98">
         <v>36</v>
@@ -9323,45 +9323,45 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M98">
-        <v>112.76928</v>
+        <v>133.80471</v>
       </c>
       <c r="N98">
-        <v>-56.16928000000001</v>
+        <v>-77.20471000000001</v>
       </c>
       <c r="O98">
-        <v>-14.04232</v>
+        <v>-19.3011775</v>
       </c>
       <c r="P98">
-        <v>-42.12696000000001</v>
+        <v>-57.9035325</v>
       </c>
       <c r="Q98">
-        <v>-20.12696000000001</v>
+        <v>-35.9035325</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8487079951911718</v>
+        <v>1.138106515027821</v>
       </c>
       <c r="T98">
-        <v>12.42073133026576</v>
+        <v>16.8976343923803</v>
       </c>
       <c r="U98">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1254774349893872</v>
+        <v>0.1057511353673574</v>
       </c>
       <c r="W98">
-        <v>0.1756041310541311</v>
+        <v>0.2108638822803771</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.5019097399575486</v>
+        <v>0.4230045414694296</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2386811612628005</v>
+        <v>0.2405811612628005</v>
       </c>
       <c r="C99">
-        <v>-414.8061497159907</v>
+        <v>-421.7583252960243</v>
       </c>
       <c r="D99">
-        <v>116.6438502840092</v>
+        <v>115.5416747039756</v>
       </c>
       <c r="E99">
-        <v>498.8499999999999</v>
+        <v>504.6999999999999</v>
       </c>
       <c r="F99">
-        <v>567.4499999999999</v>
+        <v>573.3</v>
       </c>
       <c r="G99">
         <v>36</v>
@@ -9405,37 +9405,37 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M99">
-        <v>133.80471</v>
+        <v>135.18414</v>
       </c>
       <c r="N99">
-        <v>-77.20471000000001</v>
+        <v>-78.58413999999999</v>
       </c>
       <c r="O99">
-        <v>-19.3011775</v>
+        <v>-19.646035</v>
       </c>
       <c r="P99">
-        <v>-57.9035325</v>
+        <v>-58.93810499999999</v>
       </c>
       <c r="Q99">
-        <v>-35.9035325</v>
+        <v>-36.93810499999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.138106515027821</v>
+        <v>1.684259772541731</v>
       </c>
       <c r="T99">
-        <v>16.8976343923803</v>
+        <v>25.34645158857044</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1057511353673574</v>
+        <v>0.1046720421493231</v>
       </c>
       <c r="W99">
-        <v>0.2108638822803771</v>
+        <v>0.2111183324611896</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4230045414694296</v>
+        <v>0.4186881685972925</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2405811612628005</v>
+        <v>0.2424811612628004</v>
       </c>
       <c r="C100">
-        <v>-421.7583252960243</v>
+        <v>-428.6898667867065</v>
       </c>
       <c r="D100">
-        <v>115.5416747039756</v>
+        <v>114.4601332132935</v>
       </c>
       <c r="E100">
-        <v>504.6999999999999</v>
+        <v>510.55</v>
       </c>
       <c r="F100">
-        <v>573.3</v>
+        <v>579.15</v>
       </c>
       <c r="G100">
         <v>36</v>
@@ -9487,37 +9487,37 @@
         <v>56.59999999999999</v>
       </c>
       <c r="M100">
-        <v>135.18414</v>
+        <v>136.56357</v>
       </c>
       <c r="N100">
-        <v>-78.58413999999999</v>
+        <v>-79.96357</v>
       </c>
       <c r="O100">
-        <v>-19.646035</v>
+        <v>-19.9908925</v>
       </c>
       <c r="P100">
-        <v>-58.93810499999999</v>
+        <v>-59.9726775</v>
       </c>
       <c r="Q100">
-        <v>-36.93810499999999</v>
+        <v>-37.9726775</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.684259772541731</v>
+        <v>3.322719545083462</v>
       </c>
       <c r="T100">
-        <v>25.34645158857044</v>
+        <v>50.69290317714088</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1046720421493231</v>
+        <v>0.1036147487942795</v>
       </c>
       <c r="W100">
-        <v>0.2111183324611896</v>
+        <v>0.2113676422343089</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4186881685972925</v>
+        <v>0.4144589951771178</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2424811612628004</v>
-      </c>
-      <c r="C101">
-        <v>-428.6898667867065</v>
-      </c>
-      <c r="D101">
-        <v>114.4601332132935</v>
-      </c>
-      <c r="E101">
-        <v>510.55</v>
-      </c>
-      <c r="F101">
-        <v>579.15</v>
-      </c>
-      <c r="G101">
-        <v>36</v>
-      </c>
-      <c r="H101">
-        <v>516.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>78.59999999999999</v>
-      </c>
-      <c r="K101">
-        <v>22</v>
-      </c>
-      <c r="L101">
-        <v>56.59999999999999</v>
-      </c>
-      <c r="M101">
-        <v>136.56357</v>
-      </c>
-      <c r="N101">
-        <v>-79.96357</v>
-      </c>
-      <c r="O101">
-        <v>-19.9908925</v>
-      </c>
-      <c r="P101">
-        <v>-59.9726775</v>
-      </c>
-      <c r="Q101">
-        <v>-37.9726775</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.322719545083462</v>
-      </c>
-      <c r="T101">
-        <v>50.69290317714088</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1036147487942795</v>
-      </c>
-      <c r="W101">
-        <v>0.2113676422343089</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4144589951771178</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
